--- a/output/central_unit_requests/CFOG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CFOG - SR26 sustainability reporting request.xlsx
@@ -644,7 +644,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.12)</t>
+          <t>End-2026 target status assessment and reporting (v0.13)</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (click the ref to see your full SR25 response)</t>
+          <t>SR25 response</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (click the ref to see your full SR25 response)</t>
+          <t>SR25 response</t>
         </is>
       </c>
       <c r="L26" s="13" t="inlineStr">
@@ -1447,12 +1447,10 @@
     <row r="30"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="13">
+  <mergeCells count="11">
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="H13:K13"/>
     <mergeCell ref="B4:C8"/>
     <mergeCell ref="M6:N6"/>
-    <mergeCell ref="H26:K26"/>
     <mergeCell ref="L13:R13"/>
     <mergeCell ref="L26:R26"/>
     <mergeCell ref="M5:N5"/>

--- a/output/central_unit_requests/CFOG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CFOG - SR26 sustainability reporting request.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -104,18 +104,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <i val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <sz val="22"/>
@@ -133,8 +121,12 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -159,11 +151,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C1E4F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -199,25 +186,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -230,7 +210,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -246,9 +226,10 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -634,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R30"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -648,13 +629,12 @@
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -665,455 +645,380 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.13)</t>
+          <t>SR26 sustainability reporting (v0.14)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>End-2026 target status confirmation and reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Target status assessment and definitions</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="B4" s="5" t="inlineStr">
+          <t>SR26 sustainability reporting request</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>• Confirm target status for each row below (Column L). Refer to target status definitions to the right for guidance.
-• Provide commentary on progress towards each target (Column M or N)
-• Provide supporting documentation if required (Column O), including links to images
-• Note the source of your information and any limitations (Column P), then confirm the information is accurate (Columns Q–R)
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
+• Provide supporting information if required (Column N), including links to documents or images
+• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
-• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch.
+• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
 • Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided demonstrates that the Faculty/Portfolio has met or exceeded the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided indicates that the target has not been met, but there has been a significant improvement and performance is trending towards the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>Some action has been taken to address the target, but the data and information provided demonstrates that this has been insufficient to meet the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>No action has been taken.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="L8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>Note: target status definitions are under review for 2027 reporting. 2026 ratings are for internal management reporting only.</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8" ht="60" customHeight="1"/>
     <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>CFOG – Procurement</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>Confirm end-2026 target status</t>
-        </is>
-      </c>
-      <c r="M14" s="15" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="N14" s="15" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="O14" s="15" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="P14" s="15" t="inlineStr">
+      <c r="O14" s="10" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="Q14" s="15" t="inlineStr">
+      <c r="P14" s="10" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="R14" s="15" t="inlineStr">
+      <c r="Q14" s="10" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr"/>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>(Met or exceeded; partially met; not met; not yet started)</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-A general update on activities in relation to the overarching target (Column D)</t>
-        </is>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-Data and commentary in direct response to the reporting request (Column F)</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>Provide any additional information to support the target status assessment (e.g. links, images, rationale for selection of target status)</t>
-        </is>
-      </c>
-      <c r="P15" s="16" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="inlineStr"/>
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>A general update on activities in relation to the overarching target (Column D)</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Data and commentary in direct response to the reporting request (Column F)</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Any additional information (e.g. links, images, documents)</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="Q15" s="16" t="inlineStr">
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="R15" s="16" t="inlineStr">
+      <c r="Q15" s="11" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>TR3(b)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>Please describe any efforts within your Faculty/Portfolio to make research practices more sustainable, could include examples from laboratories, fieldwork, procurement, research travel or infrastructure use. Where available, provide evidence of uptake, resource savings, emissions reductions or other outcomes.</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
-      <c r="H16" s="19" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I16" s="19" t="inlineStr"/>
-      <c r="J16" s="19" t="inlineStr"/>
-      <c r="K16" s="19" t="inlineStr"/>
-      <c r="L16" s="20" t="n"/>
-      <c r="M16" s="20" t="n"/>
-      <c r="N16" s="20" t="n"/>
-      <c r="O16" s="20" t="n"/>
-      <c r="P16" s="20" t="n"/>
-      <c r="Q16" s="20" t="n"/>
-      <c r="R16" s="20" t="n"/>
+      <c r="I16" s="14" t="inlineStr"/>
+      <c r="J16" s="14" t="inlineStr"/>
+      <c r="K16" s="14" t="inlineStr"/>
+      <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="n"/>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="15" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>NB2(c)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Nature and biodiversity</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Improve our understanding of our supply chain impacts on nature.</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Evidence of prioritised high risk procurement categories or suppliers for nature impact management</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>Please provide the prioritised high-risk procurement categories and/or suppliers identified for nature-impact management, could include the basis for prioritisation and any risk-management, engagement or mitigation actions undertaken or planned.</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>We will report on the high-risk procurement categories or suppliers prioritised for nature-impact management, and related actions, in the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H17" s="19" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I17" s="19" t="inlineStr"/>
-      <c r="J17" s="19" t="inlineStr"/>
-      <c r="K17" s="19" t="inlineStr"/>
-      <c r="L17" s="20" t="n"/>
-      <c r="M17" s="20" t="n"/>
-      <c r="N17" s="20" t="n"/>
-      <c r="O17" s="20" t="n"/>
-      <c r="P17" s="20" t="n"/>
-      <c r="Q17" s="20" t="n"/>
-      <c r="R17" s="20" t="n"/>
+      <c r="I17" s="14" t="inlineStr"/>
+      <c r="J17" s="14" t="inlineStr"/>
+      <c r="K17" s="14" t="inlineStr"/>
+      <c r="L17" s="15" t="n"/>
+      <c r="M17" s="15" t="n"/>
+      <c r="N17" s="15" t="n"/>
+      <c r="O17" s="15" t="n"/>
+      <c r="P17" s="15" t="n"/>
+      <c r="Q17" s="15" t="n"/>
     </row>
     <row r="18" ht="150" customHeight="1">
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>RP1(a)</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Responsible procurement</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Strengthen our ethical and sustainable procurement approach.</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Case studies of maturity improvement related to responsible procurement process and systems.</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 11c(iii) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your area reported on the related SP2030 target 11c(iii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Maturity score if framework established; % procurement staff trained</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>We will use case studies (and any maturity score or training data) to show improvement in responsible procurement processes and systems in the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr">
         <is>
           <t>11c(iii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I18" s="19" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J18" s="19" t="inlineStr">
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>From Matt (20/1/26): This has not changed from prior years, are you able to use what we submitted last report? (RH note: Yes we can use this).
 From Matt (28/1/26): In 2025 we increased the University’s systemic approach e.g. embedding more outcome focus questions in tenders, enhancing Modern Slavery clauses, implementing a system approach to collecting subcontracted impact spend.</t>
         </is>
       </c>
-      <c r="K18" s="19" t="inlineStr"/>
-      <c r="L18" s="20" t="n"/>
-      <c r="M18" s="20" t="n"/>
-      <c r="N18" s="20" t="n"/>
-      <c r="O18" s="20" t="n"/>
-      <c r="P18" s="20" t="n"/>
-      <c r="Q18" s="20" t="n"/>
-      <c r="R18" s="20" t="n"/>
+      <c r="K18" s="14" t="inlineStr"/>
+      <c r="L18" s="15" t="n"/>
+      <c r="M18" s="15" t="n"/>
+      <c r="N18" s="15" t="n"/>
+      <c r="O18" s="15" t="n"/>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="15" t="n"/>
     </row>
     <row r="19" ht="150" customHeight="1">
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>MS1(a)</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Modern slavery and human rights</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Manage our approach to modern slavery and human rights-related risks and opportunities.</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Annual progress reporting via the Modern Slavery Statement</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 11c(i) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your area reported on the related SP2030 target 11c(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Annual Modern Slavery Statement, with case studies</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>We will draw on the annual Modern Slavery Statement and case studies to report on the University's approach to modern slavery and human rights risks (timing to be aligned with the Statement).</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>11c(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I19" s="19" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J19" s="19" t="inlineStr">
+      <c r="J19" s="14" t="inlineStr">
         <is>
           <t>From Matt (20/1/26): Link to Annual Modern Slavery Statement; case study excerpt
 Link: https://modernslaveryregister.gov.au/statements/22714/
@@ -1121,356 +1026,329 @@
 In regard to what new information we are Ok with publishing on MS in regard to 2025 our approach is to collate this and have it approved for external consumption via this process.</t>
         </is>
       </c>
-      <c r="K19" s="19" t="inlineStr"/>
-      <c r="L19" s="20" t="n"/>
-      <c r="M19" s="20" t="n"/>
-      <c r="N19" s="20" t="n"/>
-      <c r="O19" s="20" t="n"/>
-      <c r="P19" s="20" t="n"/>
-      <c r="Q19" s="20" t="n"/>
-      <c r="R19" s="20" t="n"/>
+      <c r="K19" s="14" t="inlineStr"/>
+      <c r="L19" s="15" t="n"/>
+      <c r="M19" s="15" t="n"/>
+      <c r="N19" s="15" t="n"/>
+      <c r="O19" s="15" t="n"/>
+      <c r="P19" s="15" t="n"/>
+      <c r="Q19" s="15" t="n"/>
     </row>
     <row r="20" ht="150" customHeight="1">
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr"/>
-      <c r="J20" s="19" t="inlineStr"/>
-      <c r="K20" s="19" t="inlineStr"/>
-      <c r="L20" s="20" t="n"/>
-      <c r="M20" s="20" t="n"/>
-      <c r="N20" s="20" t="n"/>
-      <c r="O20" s="20" t="n"/>
-      <c r="P20" s="20" t="n"/>
-      <c r="Q20" s="20" t="n"/>
-      <c r="R20" s="20" t="n"/>
+      <c r="I20" s="14" t="inlineStr"/>
+      <c r="J20" s="14" t="inlineStr"/>
+      <c r="K20" s="14" t="inlineStr"/>
+      <c r="L20" s="15" t="n"/>
+      <c r="M20" s="15" t="n"/>
+      <c r="N20" s="15" t="n"/>
+      <c r="O20" s="15" t="n"/>
+      <c r="P20" s="15" t="n"/>
+      <c r="Q20" s="15" t="n"/>
     </row>
     <row r="21" ht="150" customHeight="1">
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>EN1(d)</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Sustainability objectives integrated into governance and decision‑making processes, supported by transparent reporting.</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>Please provide evidence of how sustainability objectives are integrated into governance and decision-making within your Faculty/Portfolio, could include relevant committees, policies, planning or approval processes, accountability mechanisms and examples of transparent reporting.</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>We will report on how sustainability is integrated into governance and decision-making across faculties and portfolios, and use responses as a baseline for the governance enabler from 2027.</t>
         </is>
       </c>
-      <c r="H21" s="19" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I21" s="19" t="inlineStr"/>
-      <c r="J21" s="19" t="inlineStr"/>
-      <c r="K21" s="19" t="inlineStr"/>
-      <c r="L21" s="20" t="n"/>
-      <c r="M21" s="20" t="n"/>
-      <c r="N21" s="20" t="n"/>
-      <c r="O21" s="20" t="n"/>
-      <c r="P21" s="20" t="n"/>
-      <c r="Q21" s="20" t="n"/>
-      <c r="R21" s="20" t="n"/>
+      <c r="I21" s="14" t="inlineStr"/>
+      <c r="J21" s="14" t="inlineStr"/>
+      <c r="K21" s="14" t="inlineStr"/>
+      <c r="L21" s="15" t="n"/>
+      <c r="M21" s="15" t="n"/>
+      <c r="N21" s="15" t="n"/>
+      <c r="O21" s="15" t="n"/>
+      <c r="P21" s="15" t="n"/>
+      <c r="Q21" s="15" t="n"/>
     </row>
     <row r="22"/>
     <row r="24">
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>CFOG – Treasury &amp; Investments</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L26" s="13" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I27" s="14" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J27" s="14" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K27" s="14" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L27" s="15" t="inlineStr">
-        <is>
-          <t>Confirm end-2026 target status</t>
-        </is>
-      </c>
-      <c r="M27" s="15" t="inlineStr">
+      <c r="L27" s="10" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="N27" s="15" t="inlineStr">
+      <c r="M27" s="10" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="O27" s="15" t="inlineStr">
+      <c r="N27" s="10" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="P27" s="15" t="inlineStr">
+      <c r="O27" s="10" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="Q27" s="15" t="inlineStr">
+      <c r="P27" s="10" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="R27" s="15" t="inlineStr">
+      <c r="Q27" s="10" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="16" t="inlineStr"/>
-      <c r="C28" s="16" t="inlineStr"/>
-      <c r="D28" s="16" t="inlineStr"/>
-      <c r="E28" s="16" t="inlineStr"/>
-      <c r="F28" s="16" t="inlineStr"/>
-      <c r="G28" s="16" t="inlineStr"/>
-      <c r="H28" s="16" t="inlineStr"/>
-      <c r="I28" s="16" t="inlineStr"/>
-      <c r="J28" s="16" t="inlineStr"/>
-      <c r="K28" s="16" t="inlineStr"/>
-      <c r="L28" s="16" t="inlineStr">
-        <is>
-          <t>(Met or exceeded; partially met; not met; not yet started)</t>
-        </is>
-      </c>
-      <c r="M28" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-A general update on activities in relation to the overarching target (Column D)</t>
-        </is>
-      </c>
-      <c r="N28" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-Data and commentary in direct response to the reporting request (Column F)</t>
-        </is>
-      </c>
-      <c r="O28" s="16" t="inlineStr">
-        <is>
-          <t>Provide any additional information to support the target status assessment (e.g. links, images, rationale for selection of target status)</t>
-        </is>
-      </c>
-      <c r="P28" s="16" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr"/>
+      <c r="C28" s="11" t="inlineStr"/>
+      <c r="D28" s="11" t="inlineStr"/>
+      <c r="E28" s="11" t="inlineStr"/>
+      <c r="F28" s="11" t="inlineStr"/>
+      <c r="G28" s="11" t="inlineStr"/>
+      <c r="H28" s="11" t="inlineStr"/>
+      <c r="I28" s="11" t="inlineStr"/>
+      <c r="J28" s="11" t="inlineStr"/>
+      <c r="K28" s="11" t="inlineStr"/>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
+          <t>A general update on activities in relation to the overarching target (Column D)</t>
+        </is>
+      </c>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>Data and commentary in direct response to the reporting request (Column F)</t>
+        </is>
+      </c>
+      <c r="N28" s="11" t="inlineStr">
+        <is>
+          <t>Any additional information (e.g. links, images, documents)</t>
+        </is>
+      </c>
+      <c r="O28" s="11" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="Q28" s="16" t="inlineStr">
+      <c r="P28" s="11" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="R28" s="16" t="inlineStr">
+      <c r="Q28" s="11" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="29" ht="150" customHeight="1">
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>Responsible investments</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Achieve net zero financed emissions for the University’s investment portfolio by 2050.</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Continuous improvement of the reporting of the University’s sustainability-related investment profile metrics, could include investment in climate mitigation and transition solutions, and compliance with related obligations (eg UNPRI).</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 12b(i) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your area reported on the related SP2030 target 12b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Report on relevant sustainability-related investment portfolio metrics and report on how the University has complied with its related obligations
 Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
-      <c r="G29" s="19" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>We will report on sustainability-related investment portfolio metrics and the University's compliance with related obligations (e.g. UNPRI) in the Responsible investments section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="H29" s="16" t="inlineStr">
         <is>
           <t>12b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I29" s="19" t="inlineStr">
+      <c r="I29" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J29" s="19" t="inlineStr">
+      <c r="J29" s="14" t="inlineStr">
         <is>
           <t>Since 2022 the University has published its sustainability-related investment portfolio metrics including carbon intensity. Historically this has only applied to Australian &amp; International equities, but from this year we are able to also include Fixed Income &amp; Credit. Other asset classes will be included as the data relating to them becomes available and is considered reasonable. 
 While data and metrics are continuously being refined, we have met our target of enhanced transparent reporting of the investment portfolio.</t>
         </is>
       </c>
-      <c r="K29" s="19" t="inlineStr"/>
-      <c r="L29" s="20" t="n"/>
-      <c r="M29" s="20" t="n"/>
-      <c r="N29" s="20" t="n"/>
-      <c r="O29" s="20" t="n"/>
-      <c r="P29" s="20" t="n"/>
-      <c r="Q29" s="20" t="n"/>
-      <c r="R29" s="20" t="n"/>
+      <c r="K29" s="14" t="inlineStr"/>
+      <c r="L29" s="15" t="n"/>
+      <c r="M29" s="15" t="n"/>
+      <c r="N29" s="15" t="n"/>
+      <c r="O29" s="15" t="n"/>
+      <c r="P29" s="15" t="n"/>
+      <c r="Q29" s="15" t="n"/>
     </row>
     <row r="30"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="11">
-    <mergeCell ref="M7:N7"/>
+  <mergeCells count="6">
     <mergeCell ref="B4:C8"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="L13:R13"/>
-    <mergeCell ref="L26:R26"/>
-    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="L26:Q26"/>
+    <mergeCell ref="C13:G13"/>
     <mergeCell ref="D4:G8"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="M4:N4"/>
     <mergeCell ref="C26:G26"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="L16:L21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$B$3:$B$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q16:Q21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="P16:P21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
-    <dataValidation sqref="L29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$B$3:$B$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+    <dataValidation sqref="P29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -1512,7 +1390,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting</t>
+          <t>SR26 sustainability reporting</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1402,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
@@ -1537,77 +1415,77 @@
     </row>
     <row r="6"/>
     <row r="8">
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="24" t="inlineStr"/>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr"/>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="20" t="n"/>
-      <c r="F10" s="20" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="20" t="n"/>
-      <c r="C11" s="20" t="n"/>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="20" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1658,116 +1536,116 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Procurement</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>The University has curated living labs covering the priority areas of this Plan</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Please describe any activities in Procurement which address sustainability issues via collaboration between academic and professional staff.</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr"/>
-      <c r="G7" s="19" t="inlineStr"/>
-      <c r="H7" s="19" t="inlineStr"/>
-      <c r="I7" s="19" t="inlineStr"/>
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="14" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr"/>
+      <c r="I7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>11a(iii)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>The University has reduced waste to landfill to 10kg per person</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Case studies on end of life pathways for specialist university waste streams in 2025 (e.g. the lab equipment auction organised by Procurement c. 2023)</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Not provided (as agreed with Sustainability Strategy team)</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>From Jose:
 At the moment we do not track any reduction of waste in our operation. 
@@ -1777,62 +1655,62 @@
 In our space Tom Atta or Peter Sritharan would be able to confirm or guide internally who to talk to to confirm this initiative. The potential suppliers that are doing this are CompNow and/or Citadel or others in the AV Space.</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr"/>
-      <c r="H8" s="19" t="inlineStr"/>
-      <c r="I8" s="19" t="inlineStr"/>
+      <c r="G8" s="14" t="inlineStr"/>
+      <c r="H8" s="14" t="inlineStr"/>
+      <c r="I8" s="14" t="inlineStr"/>
     </row>
     <row r="9" ht="160" customHeight="1">
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>11b(iv)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>The University has reduced the flow and improved the circularity of materials passing through the University</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Case studies demonstrating waste and/or circular economy innovation</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Not provided (as agreed with Sustainability Strategy team)</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>RH note: Not provided, but not critical for reporting.</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr"/>
-      <c r="H9" s="19" t="inlineStr"/>
-      <c r="I9" s="19" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>11c(i)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>The University has principles for ethical and sustainable consumption and service provision embedded into operations and procurement practices</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Link to Annual Modern Slavery Statement; case study excerpt</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>From Matt (20/1/26): Link to Annual Modern Slavery Statement; case study excerpt
 Link: https://modernslaveryregister.gov.au/statements/22714/
@@ -1840,101 +1718,101 @@
 In regard to what new information we are Ok with publishing on MS in regard to 2025 our approach is to collate this and have it approved for external consumption via this process.</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr"/>
-      <c r="H10" s="19" t="inlineStr"/>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr"/>
+      <c r="H10" s="14" t="inlineStr"/>
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>MS1(a)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="160" customHeight="1">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>11c(ii)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>The University has principles for ethical and sustainable consumption and service provision embedded into operations and procurement practices</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>List of Fair Trade and other relevant third-party certifications</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Not provided (as agreed with Sustainability Strategy team)</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>RH note: Not provided, but not critical for reporting</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr"/>
-      <c r="H11" s="19" t="inlineStr"/>
-      <c r="I11" s="19" t="inlineStr"/>
+      <c r="G11" s="14" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr"/>
+      <c r="I11" s="14" t="inlineStr"/>
     </row>
     <row r="12" ht="160" customHeight="1">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>11c(iii)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>The University has principles for ethical and sustainable consumption and service provision embedded into operations and procurement practices</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Description of the process for integrating supplier code of conduct into procurement practices, and key outcomes from this process.</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>From Matt (20/1/26): This has not changed from prior years, are you able to use what we submitted last report? (RH note: Yes we can use this).
 From Matt (28/1/26): In 2025 we increased the University’s systemic approach e.g. embedding more outcome focus questions in tenders, enhancing Modern Slavery clauses, implementing a system approach to collecting subcontracted impact spend.</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr"/>
-      <c r="H12" s="19" t="inlineStr"/>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr"/>
+      <c r="H12" s="14" t="inlineStr"/>
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>RP1(a)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="160" customHeight="1">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>11d</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>The University tracks spend with social and Indigenous suppliers, setting targets from 2024</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>Dollars spent with suppliers that are classified as social and/or Indigenous supplies (for example, demonstrated by listings on Supply Nation, Social Traders etc) as a percentage of total spend</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>From Matt (20/1/26): As mentioned, due to integration issues with the ERP rollout we will only get direct spend data information at the end of this month (I don’t have an exact ETA yet).
 For the indirect spend (Indigenous/ Social impact suppliers hired via our primary suppliers) this is collated quarterly and Jase is planning on having the 2025 total figures in the next 3 weeks (the construction industry shuts down over Dec/Jan and so we have slower response times). 
@@ -1942,329 +1820,329 @@
 From Matt (28/1/26): What we need to get better at is getting closer to hitting our Indigenous and Social impact spend target (3% by 2030). We have recently created an Indigenous Procurement Working Group made up of key University decision makers to better enable progress in this area.</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr"/>
-      <c r="H13" s="19" t="inlineStr"/>
-      <c r="I13" s="19" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr"/>
+      <c r="H13" s="14" t="inlineStr"/>
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>RP2(a), RP2(b)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="160" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>8a(i)</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Assessment based on the Climate Change Preparedness Framework</t>
         </is>
       </c>
-      <c r="E17" s="19" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr"/>
-      <c r="G17" s="19" t="inlineStr"/>
-      <c r="H17" s="19" t="inlineStr"/>
-      <c r="I17" s="19" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
+      <c r="G17" s="14" t="inlineStr"/>
+      <c r="H17" s="14" t="inlineStr"/>
+      <c r="I17" s="14" t="inlineStr"/>
     </row>
     <row r="18" ht="160" customHeight="1">
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>8a(ii)</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Please provide commentary regarding the Portfolio/team's level of climate change preparedness. Refer to the Climate Change Preparedness Framework for guidance: https://www.unimelb.edu.au/sustainabilityreport/domain-3-walking-the-talk-in-our-operations/climate-resilience#progress-1</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr"/>
-      <c r="G18" s="19" t="inlineStr"/>
-      <c r="H18" s="19" t="inlineStr"/>
-      <c r="I18" s="19" t="inlineStr"/>
+      <c r="F18" s="14" t="inlineStr"/>
+      <c r="G18" s="14" t="inlineStr"/>
+      <c r="H18" s="14" t="inlineStr"/>
+      <c r="I18" s="14" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>Treasury and Investments</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="160" customHeight="1">
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>12b(i)</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Enhanced transparent reporting of the University’s investment portfolio</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>Report on relevant sustainability-related investment portfolio metrics, including carbon intensity</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>Since 2022 the University has published its sustainability-related investment portfolio metrics including carbon intensity. Historically this has only applied to Australian &amp; International equities, but from this year we are able to also include Fixed Income &amp; Credit. Other asset classes will be included as the data relating to them becomes available and is considered reasonable. 
 While data and metrics are continuously being refined, we have met our target of enhanced transparent reporting of the investment portfolio.</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr"/>
-      <c r="H22" s="19" t="inlineStr"/>
-      <c r="I22" s="19" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr"/>
+      <c r="H22" s="14" t="inlineStr"/>
+      <c r="I22" s="14" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="160" customHeight="1">
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>12b(ii)</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Enhanced transparent reporting of the University’s investment portfolio</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>Reporting on how the University has complied with its related obligations</t>
         </is>
       </c>
-      <c r="E23" s="19" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>We have met the targets we set out to achieve in 2022 by being more transparent in our reporting.</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr"/>
-      <c r="H23" s="19" t="inlineStr"/>
-      <c r="I23" s="19" t="inlineStr"/>
+      <c r="G23" s="14" t="inlineStr"/>
+      <c r="H23" s="14" t="inlineStr"/>
+      <c r="I23" s="14" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>Enterprise Portfolio and Investments</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H26" s="14" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I26" s="14" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="160" customHeight="1">
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>8a(i)</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Assessment based on the Climate Change Preparedness Framework</t>
         </is>
       </c>
-      <c r="E27" s="19" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F27" s="19" t="inlineStr"/>
-      <c r="G27" s="19" t="inlineStr"/>
-      <c r="H27" s="19" t="inlineStr"/>
-      <c r="I27" s="19" t="inlineStr"/>
+      <c r="F27" s="14" t="inlineStr"/>
+      <c r="G27" s="14" t="inlineStr"/>
+      <c r="H27" s="14" t="inlineStr"/>
+      <c r="I27" s="14" t="inlineStr"/>
     </row>
     <row r="28" ht="160" customHeight="1">
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>8a(ii)</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>Please provide commentary regarding the Portfolio/team's level of climate change preparedness. Refer to the Climate Change Preparedness Framework for guidance: https://www.unimelb.edu.au/sustainabilityreport/domain-3-walking-the-talk-in-our-operations/climate-resilience#progress-1</t>
         </is>
       </c>
-      <c r="E28" s="19" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr"/>
-      <c r="G28" s="19" t="inlineStr"/>
-      <c r="H28" s="19" t="inlineStr"/>
-      <c r="I28" s="19" t="inlineStr"/>
+      <c r="F28" s="14" t="inlineStr"/>
+      <c r="G28" s="14" t="inlineStr"/>
+      <c r="H28" s="14" t="inlineStr"/>
+      <c r="I28" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2322,1331 +2200,1331 @@
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>These figures feed the Sustainability Databook (the University's authoritative quantitative source). Previous years are shown for context – please do not alter. Please provide the CY2026 value (provisional or year-to-date figures are fine; we will confirm final figures with you in January–February), the data source, and any change to definition or boundary. Due: Tuesday 15 December 2026.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Context only (please do not alter)</t>
         </is>
       </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>Please fill in these cells</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>CY2023</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>CY2024</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>CY2025</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
-      <c r="K6" s="15" t="inlineStr">
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>CY2026 value</t>
         </is>
       </c>
-      <c r="L6" s="15" t="inlineStr">
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>Data source (file name, link or system)</t>
         </is>
       </c>
-      <c r="M6" s="15" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>Change to definition or boundary?</t>
         </is>
       </c>
-      <c r="N6" s="15" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>Notes / limitations</t>
         </is>
       </c>
-      <c r="O6" s="15" t="inlineStr">
+      <c r="O6" s="10" t="inlineStr">
         <is>
           <t>Useful case studies</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>No instructions – context only.</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr"/>
-      <c r="D7" s="27" t="inlineStr"/>
-      <c r="E7" s="27" t="inlineStr"/>
-      <c r="F7" s="27" t="inlineStr"/>
-      <c r="G7" s="27" t="inlineStr"/>
-      <c r="H7" s="27" t="inlineStr"/>
-      <c r="I7" s="27" t="inlineStr"/>
-      <c r="J7" s="27" t="inlineStr"/>
-      <c r="K7" s="27" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr"/>
+      <c r="D7" s="23" t="inlineStr"/>
+      <c r="E7" s="23" t="inlineStr"/>
+      <c r="F7" s="23" t="inlineStr"/>
+      <c r="G7" s="23" t="inlineStr"/>
+      <c r="H7" s="23" t="inlineStr"/>
+      <c r="I7" s="23" t="inlineStr"/>
+      <c r="J7" s="23" t="inlineStr"/>
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>Please enter numerical values</t>
         </is>
       </c>
-      <c r="L7" s="27" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t>Please provide a file name or link to the data source</t>
         </is>
       </c>
-      <c r="M7" s="27" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>Describe any change since last year (or 'No change')</t>
         </is>
       </c>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
         <is>
           <t>Please add any additional notes here</t>
         </is>
       </c>
-      <c r="O7" s="27" t="inlineStr">
+      <c r="O7" s="23" t="inlineStr">
         <is>
           <t>Please provide information on any useful case studies</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>RP2(a)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>Percentage of Indigeneous spend of total addressable procurement spend</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Total procurement spending</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F8" s="28" t="n"/>
-      <c r="G8" s="28" t="n"/>
-      <c r="H8" s="28" t="n"/>
-      <c r="I8" s="28" t="n"/>
-      <c r="J8" s="19" t="inlineStr">
+      <c r="F8" s="24" t="n"/>
+      <c r="G8" s="24" t="n"/>
+      <c r="H8" s="24" t="n"/>
+      <c r="I8" s="24" t="n"/>
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K8" s="20" t="n"/>
-      <c r="L8" s="20" t="n"/>
-      <c r="M8" s="20" t="n"/>
-      <c r="N8" s="20" t="n"/>
-      <c r="O8" s="20" t="n"/>
+      <c r="K8" s="15" t="n"/>
+      <c r="L8" s="15" t="n"/>
+      <c r="M8" s="15" t="n"/>
+      <c r="N8" s="15" t="n"/>
+      <c r="O8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>RP2(a)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr"/>
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Total Indigeneous spending</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F9" s="28" t="n"/>
-      <c r="G9" s="28" t="n"/>
-      <c r="H9" s="28" t="n"/>
-      <c r="I9" s="28" t="n"/>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="F9" s="24" t="n"/>
+      <c r="G9" s="24" t="n"/>
+      <c r="H9" s="24" t="n"/>
+      <c r="I9" s="24" t="n"/>
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K9" s="19" t="n"/>
-      <c r="L9" s="19" t="n"/>
-      <c r="M9" s="19" t="n"/>
-      <c r="N9" s="19" t="n"/>
-      <c r="O9" s="19" t="n"/>
+      <c r="K9" s="14" t="n"/>
+      <c r="L9" s="14" t="n"/>
+      <c r="M9" s="14" t="n"/>
+      <c r="N9" s="14" t="n"/>
+      <c r="O9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>RP2(a)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr"/>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr"/>
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Percentage of Indigeneous spend of total addressable procurement spend</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F10" s="28" t="n"/>
-      <c r="G10" s="28" t="n"/>
-      <c r="H10" s="28" t="n"/>
-      <c r="I10" s="28" t="n"/>
-      <c r="J10" s="19" t="inlineStr">
+      <c r="F10" s="24" t="n"/>
+      <c r="G10" s="24" t="n"/>
+      <c r="H10" s="24" t="n"/>
+      <c r="I10" s="24" t="n"/>
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K10" s="19" t="n"/>
-      <c r="L10" s="19" t="n"/>
-      <c r="M10" s="19" t="n"/>
-      <c r="N10" s="19" t="n"/>
-      <c r="O10" s="19" t="n"/>
+      <c r="K10" s="14" t="n"/>
+      <c r="L10" s="14" t="n"/>
+      <c r="M10" s="14" t="n"/>
+      <c r="N10" s="14" t="n"/>
+      <c r="O10" s="14" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>RP2(b)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>Percentage of social spend of total addressable procurement spend</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Total procurement spending</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F11" s="28" t="n"/>
-      <c r="G11" s="28" t="n"/>
-      <c r="H11" s="28" t="n"/>
-      <c r="I11" s="28" t="n"/>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
+      <c r="H11" s="24" t="n"/>
+      <c r="I11" s="24" t="n"/>
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K11" s="20" t="n"/>
-      <c r="L11" s="20" t="n"/>
-      <c r="M11" s="20" t="n"/>
-      <c r="N11" s="20" t="n"/>
-      <c r="O11" s="20" t="n"/>
+      <c r="K11" s="15" t="n"/>
+      <c r="L11" s="15" t="n"/>
+      <c r="M11" s="15" t="n"/>
+      <c r="N11" s="15" t="n"/>
+      <c r="O11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>RP2(b)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr"/>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr"/>
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Total social spending</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F12" s="28" t="n"/>
-      <c r="G12" s="28" t="n"/>
-      <c r="H12" s="28" t="n"/>
-      <c r="I12" s="28" t="n"/>
-      <c r="J12" s="19" t="inlineStr">
+      <c r="F12" s="24" t="n"/>
+      <c r="G12" s="24" t="n"/>
+      <c r="H12" s="24" t="n"/>
+      <c r="I12" s="24" t="n"/>
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K12" s="19" t="n"/>
-      <c r="L12" s="19" t="n"/>
-      <c r="M12" s="19" t="n"/>
-      <c r="N12" s="19" t="n"/>
-      <c r="O12" s="19" t="n"/>
+      <c r="K12" s="14" t="n"/>
+      <c r="L12" s="14" t="n"/>
+      <c r="M12" s="14" t="n"/>
+      <c r="N12" s="14" t="n"/>
+      <c r="O12" s="14" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>RP2(b)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr"/>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr"/>
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>Percentage of Indigeneous spend of total addressable procurement spend</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F13" s="28" t="n"/>
-      <c r="G13" s="28" t="n"/>
-      <c r="H13" s="28" t="n"/>
-      <c r="I13" s="28" t="n"/>
-      <c r="J13" s="19" t="inlineStr">
+      <c r="F13" s="24" t="n"/>
+      <c r="G13" s="24" t="n"/>
+      <c r="H13" s="24" t="n"/>
+      <c r="I13" s="24" t="n"/>
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K13" s="19" t="n"/>
-      <c r="L13" s="19" t="n"/>
-      <c r="M13" s="19" t="n"/>
-      <c r="N13" s="19" t="n"/>
-      <c r="O13" s="19" t="n"/>
+      <c r="K13" s="14" t="n"/>
+      <c r="L13" s="14" t="n"/>
+      <c r="M13" s="14" t="n"/>
+      <c r="N13" s="14" t="n"/>
+      <c r="O13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>RI1(a)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Annual monitoring and reporting on the investment portfolio's net zero transition progress, including tracking the percentage of AUM managed by investment managers aligned with (or commited to net zero by 2050</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Total Asset Under Management (AUM)</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F14" s="28" t="n"/>
-      <c r="G14" s="28" t="n"/>
-      <c r="H14" s="28" t="n"/>
-      <c r="I14" s="28" t="n"/>
-      <c r="J14" s="19" t="inlineStr">
+      <c r="F14" s="24" t="n"/>
+      <c r="G14" s="24" t="n"/>
+      <c r="H14" s="24" t="n"/>
+      <c r="I14" s="24" t="n"/>
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K14" s="20" t="n"/>
-      <c r="L14" s="20" t="n"/>
-      <c r="M14" s="20" t="n"/>
-      <c r="N14" s="20" t="n"/>
-      <c r="O14" s="20" t="n"/>
+      <c r="K14" s="15" t="n"/>
+      <c r="L14" s="15" t="n"/>
+      <c r="M14" s="15" t="n"/>
+      <c r="N14" s="15" t="n"/>
+      <c r="O14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>RI1(a)</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr"/>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr"/>
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>AUM managed by Investment Managers aligned with net zero commitment</t>
         </is>
       </c>
-      <c r="E15" s="19" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="28" t="n"/>
-      <c r="H15" s="28" t="n"/>
-      <c r="I15" s="28" t="n"/>
-      <c r="J15" s="19" t="inlineStr">
+      <c r="F15" s="24" t="n"/>
+      <c r="G15" s="24" t="n"/>
+      <c r="H15" s="24" t="n"/>
+      <c r="I15" s="24" t="n"/>
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K15" s="19" t="n"/>
-      <c r="L15" s="19" t="n"/>
-      <c r="M15" s="19" t="n"/>
-      <c r="N15" s="19" t="n"/>
-      <c r="O15" s="19" t="n"/>
+      <c r="K15" s="14" t="n"/>
+      <c r="L15" s="14" t="n"/>
+      <c r="M15" s="14" t="n"/>
+      <c r="N15" s="14" t="n"/>
+      <c r="O15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>RI1(a)</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr"/>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr"/>
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Percentage of AUM managed by Investment Managers aligned with net zero commitment</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F16" s="28" t="n"/>
-      <c r="G16" s="28" t="n"/>
-      <c r="H16" s="28" t="n"/>
-      <c r="I16" s="28" t="n"/>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="F16" s="24" t="n"/>
+      <c r="G16" s="24" t="n"/>
+      <c r="H16" s="24" t="n"/>
+      <c r="I16" s="24" t="n"/>
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K16" s="19" t="n"/>
-      <c r="L16" s="19" t="n"/>
-      <c r="M16" s="19" t="n"/>
-      <c r="N16" s="19" t="n"/>
-      <c r="O16" s="19" t="n"/>
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>Continuous improvement of the reporting of the University's sustainability-related investment profile metrics, including investment in climate mitigation and transition solutions, and compliance with related obligations (e.g. UNPRI)</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Total Asset Under Management (AUM)</t>
         </is>
       </c>
-      <c r="E17" s="19" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F17" s="28" t="n"/>
-      <c r="G17" s="28" t="n"/>
-      <c r="H17" s="28" t="n"/>
-      <c r="I17" s="28" t="n"/>
-      <c r="J17" s="19" t="inlineStr">
+      <c r="F17" s="24" t="n"/>
+      <c r="G17" s="24" t="n"/>
+      <c r="H17" s="24" t="n"/>
+      <c r="I17" s="24" t="n"/>
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K17" s="20" t="n"/>
-      <c r="L17" s="20" t="n"/>
-      <c r="M17" s="20" t="n"/>
-      <c r="N17" s="20" t="n"/>
-      <c r="O17" s="20" t="n"/>
+      <c r="K17" s="15" t="n"/>
+      <c r="L17" s="15" t="n"/>
+      <c r="M17" s="15" t="n"/>
+      <c r="N17" s="15" t="n"/>
+      <c r="O17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr"/>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr"/>
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>AUM invested in climate/transition solution</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F18" s="28" t="n"/>
-      <c r="G18" s="28" t="n"/>
-      <c r="H18" s="28" t="n"/>
-      <c r="I18" s="28" t="n"/>
-      <c r="J18" s="19" t="inlineStr">
+      <c r="F18" s="24" t="n"/>
+      <c r="G18" s="24" t="n"/>
+      <c r="H18" s="24" t="n"/>
+      <c r="I18" s="24" t="n"/>
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K18" s="19" t="n"/>
-      <c r="L18" s="19" t="n"/>
-      <c r="M18" s="19" t="n"/>
-      <c r="N18" s="19" t="n"/>
-      <c r="O18" s="19" t="n"/>
+      <c r="K18" s="14" t="n"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
+      <c r="N18" s="14" t="n"/>
+      <c r="O18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr"/>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr"/>
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>Percentage of AUM invested in climate/transition solution</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F19" s="28" t="n"/>
-      <c r="G19" s="28" t="n"/>
-      <c r="H19" s="28" t="n"/>
-      <c r="I19" s="28" t="n"/>
-      <c r="J19" s="19" t="inlineStr">
+      <c r="F19" s="24" t="n"/>
+      <c r="G19" s="24" t="n"/>
+      <c r="H19" s="24" t="n"/>
+      <c r="I19" s="24" t="n"/>
+      <c r="J19" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K19" s="19" t="n"/>
-      <c r="L19" s="19" t="n"/>
-      <c r="M19" s="19" t="n"/>
-      <c r="N19" s="19" t="n"/>
-      <c r="O19" s="19" t="n"/>
+      <c r="K19" s="14" t="n"/>
+      <c r="L19" s="14" t="n"/>
+      <c r="M19" s="14" t="n"/>
+      <c r="N19" s="14" t="n"/>
+      <c r="O19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr"/>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr"/>
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>Estimated UoM absolute financed carbon emissions</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F20" s="28" t="n"/>
-      <c r="G20" s="28" t="n">
+      <c r="F20" s="24" t="n"/>
+      <c r="G20" s="24" t="n">
         <v>121733</v>
       </c>
-      <c r="H20" s="28" t="n">
+      <c r="H20" s="24" t="n">
         <v>111919</v>
       </c>
-      <c r="I20" s="28" t="n">
+      <c r="I20" s="24" t="n">
         <v>123381</v>
       </c>
-      <c r="J20" s="19" t="inlineStr">
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K20" s="19" t="n"/>
-      <c r="L20" s="19" t="n"/>
-      <c r="M20" s="19" t="n"/>
-      <c r="N20" s="19" t="n"/>
-      <c r="O20" s="19" t="n"/>
+      <c r="K20" s="14" t="n"/>
+      <c r="L20" s="14" t="n"/>
+      <c r="M20" s="14" t="n"/>
+      <c r="N20" s="14" t="n"/>
+      <c r="O20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr"/>
-      <c r="D21" s="29" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr"/>
+      <c r="D21" s="25" t="inlineStr">
         <is>
           <t>Australian Equities</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F21" s="28" t="n"/>
-      <c r="G21" s="28" t="n">
+      <c r="F21" s="24" t="n"/>
+      <c r="G21" s="24" t="n">
         <v>101663</v>
       </c>
-      <c r="H21" s="28" t="n">
+      <c r="H21" s="24" t="n">
         <v>82052</v>
       </c>
-      <c r="I21" s="28" t="n">
+      <c r="I21" s="24" t="n">
         <v>57483</v>
       </c>
-      <c r="J21" s="19" t="inlineStr">
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K21" s="19" t="n"/>
-      <c r="L21" s="19" t="n"/>
-      <c r="M21" s="19" t="n"/>
-      <c r="N21" s="19" t="n"/>
-      <c r="O21" s="19" t="n"/>
+      <c r="K21" s="14" t="n"/>
+      <c r="L21" s="14" t="n"/>
+      <c r="M21" s="14" t="n"/>
+      <c r="N21" s="14" t="n"/>
+      <c r="O21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr"/>
-      <c r="D22" s="29" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr"/>
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>International Equities</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F22" s="28" t="n"/>
-      <c r="G22" s="28" t="n">
+      <c r="F22" s="24" t="n"/>
+      <c r="G22" s="24" t="n">
         <v>20070</v>
       </c>
-      <c r="H22" s="28" t="n">
+      <c r="H22" s="24" t="n">
         <v>29867</v>
       </c>
-      <c r="I22" s="28" t="n">
+      <c r="I22" s="24" t="n">
         <v>27910</v>
       </c>
-      <c r="J22" s="19" t="inlineStr">
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K22" s="19" t="n"/>
-      <c r="L22" s="19" t="n"/>
-      <c r="M22" s="19" t="n"/>
-      <c r="N22" s="19" t="n"/>
-      <c r="O22" s="19" t="n"/>
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="14" t="n"/>
+      <c r="N22" s="14" t="n"/>
+      <c r="O22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr"/>
-      <c r="D23" s="29" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr"/>
+      <c r="D23" s="25" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E23" s="19" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F23" s="28" t="n"/>
-      <c r="G23" s="28" t="inlineStr">
+      <c r="F23" s="24" t="n"/>
+      <c r="G23" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H23" s="28" t="inlineStr">
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I23" s="28" t="n">
+      <c r="I23" s="24" t="n">
         <v>9312</v>
       </c>
-      <c r="J23" s="19" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K23" s="19" t="n"/>
-      <c r="L23" s="19" t="n"/>
-      <c r="M23" s="19" t="n"/>
-      <c r="N23" s="19" t="n"/>
-      <c r="O23" s="19" t="n"/>
+      <c r="K23" s="14" t="n"/>
+      <c r="L23" s="14" t="n"/>
+      <c r="M23" s="14" t="n"/>
+      <c r="N23" s="14" t="n"/>
+      <c r="O23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr"/>
-      <c r="D24" s="29" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr"/>
+      <c r="D24" s="25" t="inlineStr">
         <is>
           <t>Fixed Interest</t>
         </is>
       </c>
-      <c r="E24" s="19" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F24" s="28" t="n"/>
-      <c r="G24" s="28" t="inlineStr">
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H24" s="28" t="inlineStr">
+      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I24" s="28" t="n">
+      <c r="I24" s="24" t="n">
         <v>28676</v>
       </c>
-      <c r="J24" s="19" t="inlineStr">
+      <c r="J24" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K24" s="19" t="n"/>
-      <c r="L24" s="19" t="n"/>
-      <c r="M24" s="19" t="n"/>
-      <c r="N24" s="19" t="n"/>
-      <c r="O24" s="19" t="n"/>
+      <c r="K24" s="14" t="n"/>
+      <c r="L24" s="14" t="n"/>
+      <c r="M24" s="14" t="n"/>
+      <c r="N24" s="14" t="n"/>
+      <c r="O24" s="14" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr"/>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr"/>
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>Estimated UoM absolute financed carbon emissions intensity</t>
         </is>
       </c>
-      <c r="E25" s="19" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F25" s="28" t="n"/>
-      <c r="G25" s="28" t="n">
+      <c r="F25" s="24" t="n"/>
+      <c r="G25" s="24" t="n">
         <v>55</v>
       </c>
-      <c r="H25" s="28" t="n">
+      <c r="H25" s="24" t="n">
         <v>49</v>
       </c>
-      <c r="I25" s="28" t="n">
+      <c r="I25" s="24" t="n">
         <v>38.2</v>
       </c>
-      <c r="J25" s="19" t="inlineStr">
+      <c r="J25" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K25" s="19" t="n"/>
-      <c r="L25" s="19" t="n"/>
-      <c r="M25" s="19" t="n"/>
-      <c r="N25" s="19" t="n"/>
-      <c r="O25" s="19" t="n"/>
+      <c r="K25" s="14" t="n"/>
+      <c r="L25" s="14" t="n"/>
+      <c r="M25" s="14" t="n"/>
+      <c r="N25" s="14" t="n"/>
+      <c r="O25" s="14" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr"/>
-      <c r="D26" s="29" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr"/>
+      <c r="D26" s="25" t="inlineStr">
         <is>
           <t>Australian Equities</t>
         </is>
       </c>
-      <c r="E26" s="19" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F26" s="28" t="n"/>
-      <c r="G26" s="28" t="n">
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="24" t="n">
         <v>94</v>
       </c>
-      <c r="H26" s="28" t="n">
+      <c r="H26" s="24" t="n">
         <v>72</v>
       </c>
-      <c r="I26" s="28" t="n">
+      <c r="I26" s="24" t="n">
         <v>52.6</v>
       </c>
-      <c r="J26" s="19" t="inlineStr">
+      <c r="J26" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K26" s="19" t="n"/>
-      <c r="L26" s="19" t="n"/>
-      <c r="M26" s="19" t="n"/>
-      <c r="N26" s="19" t="n"/>
-      <c r="O26" s="19" t="n"/>
+      <c r="K26" s="14" t="n"/>
+      <c r="L26" s="14" t="n"/>
+      <c r="M26" s="14" t="n"/>
+      <c r="N26" s="14" t="n"/>
+      <c r="O26" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr"/>
-      <c r="D27" s="29" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr"/>
+      <c r="D27" s="25" t="inlineStr">
         <is>
           <t>International Equities</t>
         </is>
       </c>
-      <c r="E27" s="19" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F27" s="28" t="n"/>
-      <c r="G27" s="28" t="n">
+      <c r="F27" s="24" t="n"/>
+      <c r="G27" s="24" t="n">
         <v>18</v>
       </c>
-      <c r="H27" s="28" t="n">
+      <c r="H27" s="24" t="n">
         <v>26</v>
       </c>
-      <c r="I27" s="28" t="n">
+      <c r="I27" s="24" t="n">
         <v>23.4</v>
       </c>
-      <c r="J27" s="19" t="inlineStr">
+      <c r="J27" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K27" s="19" t="n"/>
-      <c r="L27" s="19" t="n"/>
-      <c r="M27" s="19" t="n"/>
-      <c r="N27" s="19" t="n"/>
-      <c r="O27" s="19" t="n"/>
+      <c r="K27" s="14" t="n"/>
+      <c r="L27" s="14" t="n"/>
+      <c r="M27" s="14" t="n"/>
+      <c r="N27" s="14" t="n"/>
+      <c r="O27" s="14" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr"/>
-      <c r="D28" s="29" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr"/>
+      <c r="D28" s="25" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E28" s="19" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F28" s="28" t="n"/>
-      <c r="G28" s="28" t="inlineStr">
+      <c r="F28" s="24" t="n"/>
+      <c r="G28" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H28" s="28" t="inlineStr">
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I28" s="28" t="n">
+      <c r="I28" s="24" t="n">
         <v>43.1</v>
       </c>
-      <c r="J28" s="19" t="inlineStr">
+      <c r="J28" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K28" s="19" t="n"/>
-      <c r="L28" s="19" t="n"/>
-      <c r="M28" s="19" t="n"/>
-      <c r="N28" s="19" t="n"/>
-      <c r="O28" s="19" t="n"/>
+      <c r="K28" s="14" t="n"/>
+      <c r="L28" s="14" t="n"/>
+      <c r="M28" s="14" t="n"/>
+      <c r="N28" s="14" t="n"/>
+      <c r="O28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C29" s="19" t="inlineStr"/>
-      <c r="D29" s="29" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr"/>
+      <c r="D29" s="25" t="inlineStr">
         <is>
           <t>Fixed Interest</t>
         </is>
       </c>
-      <c r="E29" s="19" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F29" s="28" t="n"/>
-      <c r="G29" s="28" t="inlineStr">
+      <c r="F29" s="24" t="n"/>
+      <c r="G29" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H29" s="28" t="inlineStr">
+      <c r="H29" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I29" s="28" t="n">
+      <c r="I29" s="24" t="n">
         <v>54.3</v>
       </c>
-      <c r="J29" s="19" t="inlineStr">
+      <c r="J29" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K29" s="19" t="n"/>
-      <c r="L29" s="19" t="n"/>
-      <c r="M29" s="19" t="n"/>
-      <c r="N29" s="19" t="n"/>
-      <c r="O29" s="19" t="n"/>
+      <c r="K29" s="14" t="n"/>
+      <c r="L29" s="14" t="n"/>
+      <c r="M29" s="14" t="n"/>
+      <c r="N29" s="14" t="n"/>
+      <c r="O29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr"/>
-      <c r="D30" s="19" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr"/>
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>Benchmark financed carbon emissions</t>
         </is>
       </c>
-      <c r="E30" s="19" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F30" s="28" t="n"/>
-      <c r="G30" s="28" t="n">
+      <c r="F30" s="24" t="n"/>
+      <c r="G30" s="24" t="n">
         <v>103250</v>
       </c>
-      <c r="H30" s="28" t="n">
+      <c r="H30" s="24" t="n">
         <v>118609</v>
       </c>
-      <c r="I30" s="28" t="n">
+      <c r="I30" s="24" t="n">
         <v>143399</v>
       </c>
-      <c r="J30" s="19" t="inlineStr">
+      <c r="J30" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K30" s="19" t="n"/>
-      <c r="L30" s="19" t="n"/>
-      <c r="M30" s="19" t="n"/>
-      <c r="N30" s="19" t="n"/>
-      <c r="O30" s="19" t="n"/>
+      <c r="K30" s="14" t="n"/>
+      <c r="L30" s="14" t="n"/>
+      <c r="M30" s="14" t="n"/>
+      <c r="N30" s="14" t="n"/>
+      <c r="O30" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr"/>
-      <c r="D31" s="29" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr"/>
+      <c r="D31" s="25" t="inlineStr">
         <is>
           <t>Australian Equities</t>
         </is>
       </c>
-      <c r="E31" s="19" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F31" s="28" t="n"/>
-      <c r="G31" s="28" t="n">
+      <c r="F31" s="24" t="n"/>
+      <c r="G31" s="24" t="n">
         <v>62433</v>
       </c>
-      <c r="H31" s="28" t="n">
+      <c r="H31" s="24" t="n">
         <v>76031</v>
       </c>
-      <c r="I31" s="28" t="n">
+      <c r="I31" s="24" t="n">
         <v>49827</v>
       </c>
-      <c r="J31" s="19" t="inlineStr">
+      <c r="J31" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K31" s="19" t="n"/>
-      <c r="L31" s="19" t="n"/>
-      <c r="M31" s="19" t="n"/>
-      <c r="N31" s="19" t="n"/>
-      <c r="O31" s="19" t="n"/>
+      <c r="K31" s="14" t="n"/>
+      <c r="L31" s="14" t="n"/>
+      <c r="M31" s="14" t="n"/>
+      <c r="N31" s="14" t="n"/>
+      <c r="O31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C32" s="19" t="inlineStr"/>
-      <c r="D32" s="29" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr"/>
+      <c r="D32" s="25" t="inlineStr">
         <is>
           <t>International Equities</t>
         </is>
       </c>
-      <c r="E32" s="19" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F32" s="28" t="n"/>
-      <c r="G32" s="28" t="n">
+      <c r="F32" s="24" t="n"/>
+      <c r="G32" s="24" t="n">
         <v>40817</v>
       </c>
-      <c r="H32" s="28" t="n">
+      <c r="H32" s="24" t="n">
         <v>42578</v>
       </c>
-      <c r="I32" s="28" t="n">
+      <c r="I32" s="24" t="n">
         <v>34989</v>
       </c>
-      <c r="J32" s="19" t="inlineStr">
+      <c r="J32" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K32" s="19" t="n"/>
-      <c r="L32" s="19" t="n"/>
-      <c r="M32" s="19" t="n"/>
-      <c r="N32" s="19" t="n"/>
-      <c r="O32" s="19" t="n"/>
+      <c r="K32" s="14" t="n"/>
+      <c r="L32" s="14" t="n"/>
+      <c r="M32" s="14" t="n"/>
+      <c r="N32" s="14" t="n"/>
+      <c r="O32" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr"/>
-      <c r="D33" s="29" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr"/>
+      <c r="D33" s="25" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E33" s="19" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F33" s="28" t="n"/>
-      <c r="G33" s="28" t="inlineStr">
+      <c r="F33" s="24" t="n"/>
+      <c r="G33" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H33" s="28" t="inlineStr">
+      <c r="H33" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I33" s="28" t="inlineStr">
+      <c r="I33" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J33" s="19" t="inlineStr">
+      <c r="J33" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K33" s="19" t="n"/>
-      <c r="L33" s="19" t="n"/>
-      <c r="M33" s="19" t="n"/>
-      <c r="N33" s="19" t="n"/>
-      <c r="O33" s="19" t="n"/>
+      <c r="K33" s="14" t="n"/>
+      <c r="L33" s="14" t="n"/>
+      <c r="M33" s="14" t="n"/>
+      <c r="N33" s="14" t="n"/>
+      <c r="O33" s="14" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C34" s="19" t="inlineStr"/>
-      <c r="D34" s="29" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr"/>
+      <c r="D34" s="25" t="inlineStr">
         <is>
           <t>Fixed Interest</t>
         </is>
       </c>
-      <c r="E34" s="19" t="inlineStr">
+      <c r="E34" s="14" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F34" s="28" t="n"/>
-      <c r="G34" s="28" t="inlineStr">
+      <c r="F34" s="24" t="n"/>
+      <c r="G34" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H34" s="28" t="inlineStr">
+      <c r="H34" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I34" s="28" t="n">
+      <c r="I34" s="24" t="n">
         <v>58583</v>
       </c>
-      <c r="J34" s="19" t="inlineStr">
+      <c r="J34" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K34" s="19" t="n"/>
-      <c r="L34" s="19" t="n"/>
-      <c r="M34" s="19" t="n"/>
-      <c r="N34" s="19" t="n"/>
-      <c r="O34" s="19" t="n"/>
+      <c r="K34" s="14" t="n"/>
+      <c r="L34" s="14" t="n"/>
+      <c r="M34" s="14" t="n"/>
+      <c r="N34" s="14" t="n"/>
+      <c r="O34" s="14" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C35" s="19" t="inlineStr"/>
-      <c r="D35" s="19" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr"/>
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>Benchmark financed carbon emissions intensity</t>
         </is>
       </c>
-      <c r="E35" s="19" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F35" s="28" t="n"/>
-      <c r="G35" s="28" t="n">
+      <c r="F35" s="24" t="n"/>
+      <c r="G35" s="24" t="n">
         <v>47</v>
       </c>
-      <c r="H35" s="28" t="n">
+      <c r="H35" s="24" t="n">
         <v>51</v>
       </c>
-      <c r="I35" s="28" t="n">
+      <c r="I35" s="24" t="n">
         <v>48.6</v>
       </c>
-      <c r="J35" s="19" t="inlineStr">
+      <c r="J35" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K35" s="19" t="n"/>
-      <c r="L35" s="19" t="n"/>
-      <c r="M35" s="19" t="n"/>
-      <c r="N35" s="19" t="n"/>
-      <c r="O35" s="19" t="n"/>
+      <c r="K35" s="14" t="n"/>
+      <c r="L35" s="14" t="n"/>
+      <c r="M35" s="14" t="n"/>
+      <c r="N35" s="14" t="n"/>
+      <c r="O35" s="14" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr"/>
-      <c r="D36" s="29" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr"/>
+      <c r="D36" s="25" t="inlineStr">
         <is>
           <t>Australian Equities</t>
         </is>
       </c>
-      <c r="E36" s="19" t="inlineStr">
+      <c r="E36" s="14" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F36" s="28" t="n"/>
-      <c r="G36" s="28" t="n">
+      <c r="F36" s="24" t="n"/>
+      <c r="G36" s="24" t="n">
         <v>58</v>
       </c>
-      <c r="H36" s="28" t="n">
+      <c r="H36" s="24" t="n">
         <v>67</v>
       </c>
-      <c r="I36" s="28" t="n">
+      <c r="I36" s="24" t="n">
         <v>45.6</v>
       </c>
-      <c r="J36" s="19" t="inlineStr">
+      <c r="J36" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K36" s="19" t="n"/>
-      <c r="L36" s="19" t="n"/>
-      <c r="M36" s="19" t="n"/>
-      <c r="N36" s="19" t="n"/>
-      <c r="O36" s="19" t="n"/>
+      <c r="K36" s="14" t="n"/>
+      <c r="L36" s="14" t="n"/>
+      <c r="M36" s="14" t="n"/>
+      <c r="N36" s="14" t="n"/>
+      <c r="O36" s="14" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C37" s="19" t="inlineStr"/>
-      <c r="D37" s="29" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr"/>
+      <c r="D37" s="25" t="inlineStr">
         <is>
           <t>International Equities</t>
         </is>
       </c>
-      <c r="E37" s="19" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F37" s="28" t="n"/>
-      <c r="G37" s="28" t="n">
+      <c r="F37" s="24" t="n"/>
+      <c r="G37" s="24" t="n">
         <v>36</v>
       </c>
-      <c r="H37" s="28" t="n">
+      <c r="H37" s="24" t="n">
         <v>37</v>
       </c>
-      <c r="I37" s="28" t="n">
+      <c r="I37" s="24" t="n">
         <v>26</v>
       </c>
-      <c r="J37" s="19" t="inlineStr">
+      <c r="J37" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K37" s="19" t="n"/>
-      <c r="L37" s="19" t="n"/>
-      <c r="M37" s="19" t="n"/>
-      <c r="N37" s="19" t="n"/>
-      <c r="O37" s="19" t="n"/>
+      <c r="K37" s="14" t="n"/>
+      <c r="L37" s="14" t="n"/>
+      <c r="M37" s="14" t="n"/>
+      <c r="N37" s="14" t="n"/>
+      <c r="O37" s="14" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C38" s="19" t="inlineStr"/>
-      <c r="D38" s="29" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr"/>
+      <c r="D38" s="25" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E38" s="19" t="inlineStr">
+      <c r="E38" s="14" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F38" s="28" t="n"/>
-      <c r="G38" s="28" t="inlineStr">
+      <c r="F38" s="24" t="n"/>
+      <c r="G38" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H38" s="28" t="inlineStr">
+      <c r="H38" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I38" s="28" t="inlineStr">
+      <c r="I38" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J38" s="19" t="inlineStr">
+      <c r="J38" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K38" s="19" t="n"/>
-      <c r="L38" s="19" t="n"/>
-      <c r="M38" s="19" t="n"/>
-      <c r="N38" s="19" t="n"/>
-      <c r="O38" s="19" t="n"/>
+      <c r="K38" s="14" t="n"/>
+      <c r="L38" s="14" t="n"/>
+      <c r="M38" s="14" t="n"/>
+      <c r="N38" s="14" t="n"/>
+      <c r="O38" s="14" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C39" s="19" t="inlineStr"/>
-      <c r="D39" s="29" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr"/>
+      <c r="D39" s="25" t="inlineStr">
         <is>
           <t>Fixed Interest</t>
         </is>
       </c>
-      <c r="E39" s="19" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F39" s="28" t="n"/>
-      <c r="G39" s="28" t="inlineStr">
+      <c r="F39" s="24" t="n"/>
+      <c r="G39" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H39" s="28" t="inlineStr">
+      <c r="H39" s="24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I39" s="28" t="n">
+      <c r="I39" s="24" t="n">
         <v>112.9</v>
       </c>
-      <c r="J39" s="19" t="inlineStr">
+      <c r="J39" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K39" s="19" t="n"/>
-      <c r="L39" s="19" t="n"/>
-      <c r="M39" s="19" t="n"/>
-      <c r="N39" s="19" t="n"/>
-      <c r="O39" s="19" t="n"/>
+      <c r="K39" s="14" t="n"/>
+      <c r="L39" s="14" t="n"/>
+      <c r="M39" s="14" t="n"/>
+      <c r="N39" s="14" t="n"/>
+      <c r="O39" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -3670,13 +3548,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I9"/>
+  <dimension ref="B1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>End 2026 target status</t>
+          <t>(not used – no target status rating in 2026)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -3692,21 +3570,6 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Y/N</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Response count</t>
         </is>
       </c>
     </row>
@@ -3731,24 +3594,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -3764,24 +3611,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -3797,47 +3628,15 @@
           <t>TBC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
@@ -3845,11 +3644,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>

--- a/output/central_unit_requests/CFOG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CFOG - SR26 sustainability reporting request.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.14)</t>
+          <t>SR26 sustainability reporting (v0.15)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/CFOG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CFOG - SR26 sustainability reporting request.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.15)</t>
+          <t>SR26 sustainability reporting (v0.16)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/CFOG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CFOG - SR26 sustainability reporting request.xlsx
@@ -23,21 +23,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="00002060"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -186,68 +178,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -637,32 +627,22 @@
     <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting (v0.16)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -678,347 +658,350 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="60" customHeight="1"/>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11" ht="39" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>CFOG – Procurement</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="C13" s="7" t="inlineStr">
+    <row r="12"/>
+    <row r="13" ht="27" customHeight="1">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="10" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="10" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="11" t="inlineStr"/>
-      <c r="C15" s="11" t="inlineStr"/>
-      <c r="D15" s="11" t="inlineStr"/>
-      <c r="E15" s="11" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr"/>
-      <c r="G15" s="11" t="inlineStr"/>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr"/>
-      <c r="K15" s="11" t="inlineStr"/>
-      <c r="L15" s="11" t="inlineStr">
+    <row r="15" ht="81" customHeight="1">
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="P15" s="9" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q15" s="9" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>TR3(b)</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Please describe any efforts within your Faculty/Portfolio to make research practices more sustainable, could include examples from laboratories, fieldwork, procurement, research travel or infrastructure use. Where available, provide evidence of uptake, resource savings, emissions reductions or other outcomes.</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr"/>
-      <c r="J16" s="14" t="inlineStr"/>
-      <c r="K16" s="14" t="inlineStr"/>
-      <c r="L16" s="15" t="n"/>
-      <c r="M16" s="15" t="n"/>
-      <c r="N16" s="15" t="n"/>
-      <c r="O16" s="15" t="n"/>
-      <c r="P16" s="15" t="n"/>
-      <c r="Q16" s="15" t="n"/>
+      <c r="I16" s="12" t="inlineStr"/>
+      <c r="J16" s="12" t="inlineStr"/>
+      <c r="K16" s="12" t="inlineStr"/>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="13" t="n"/>
+      <c r="N16" s="13" t="n"/>
+      <c r="O16" s="13" t="n"/>
+      <c r="P16" s="13" t="n"/>
+      <c r="Q16" s="13" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>NB2(c)</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Nature and biodiversity</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Improve our understanding of our supply chain impacts on nature.</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Evidence of prioritised high risk procurement categories or suppliers for nature impact management</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Please provide the prioritised high-risk procurement categories and/or suppliers identified for nature-impact management, could include the basis for prioritisation and any risk-management, engagement or mitigation actions undertaken or planned.</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>We will report on the high-risk procurement categories or suppliers prioritised for nature-impact management, and related actions, in the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr"/>
-      <c r="J17" s="14" t="inlineStr"/>
-      <c r="K17" s="14" t="inlineStr"/>
-      <c r="L17" s="15" t="n"/>
-      <c r="M17" s="15" t="n"/>
-      <c r="N17" s="15" t="n"/>
-      <c r="O17" s="15" t="n"/>
-      <c r="P17" s="15" t="n"/>
-      <c r="Q17" s="15" t="n"/>
+      <c r="I17" s="12" t="inlineStr"/>
+      <c r="J17" s="12" t="inlineStr"/>
+      <c r="K17" s="12" t="inlineStr"/>
+      <c r="L17" s="13" t="n"/>
+      <c r="M17" s="13" t="n"/>
+      <c r="N17" s="13" t="n"/>
+      <c r="O17" s="13" t="n"/>
+      <c r="P17" s="13" t="n"/>
+      <c r="Q17" s="13" t="n"/>
     </row>
     <row r="18" ht="150" customHeight="1">
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>RP1(a)</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Responsible procurement</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Strengthen our ethical and sustainable procurement approach.</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Case studies of maturity improvement related to responsible procurement process and systems.</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your area reported on the related SP2030 target 11c(iii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Maturity score if framework established; % procurement staff trained</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>We will use case studies (and any maturity score or training data) to show improvement in responsible procurement processes and systems in the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>11c(iii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="I18" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J18" s="14" t="inlineStr">
+      <c r="J18" s="12" t="inlineStr">
         <is>
           <t>From Matt (20/1/26): This has not changed from prior years, are you able to use what we submitted last report? (RH note: Yes we can use this).
 From Matt (28/1/26): In 2025 we increased the University’s systemic approach e.g. embedding more outcome focus questions in tenders, enhancing Modern Slavery clauses, implementing a system approach to collecting subcontracted impact spend.</t>
         </is>
       </c>
-      <c r="K18" s="14" t="inlineStr"/>
-      <c r="L18" s="15" t="n"/>
-      <c r="M18" s="15" t="n"/>
-      <c r="N18" s="15" t="n"/>
-      <c r="O18" s="15" t="n"/>
-      <c r="P18" s="15" t="n"/>
-      <c r="Q18" s="15" t="n"/>
+      <c r="K18" s="12" t="inlineStr"/>
+      <c r="L18" s="13" t="n"/>
+      <c r="M18" s="13" t="n"/>
+      <c r="N18" s="13" t="n"/>
+      <c r="O18" s="13" t="n"/>
+      <c r="P18" s="13" t="n"/>
+      <c r="Q18" s="13" t="n"/>
     </row>
     <row r="19" ht="150" customHeight="1">
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>MS1(a)</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Modern slavery and human rights</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Manage our approach to modern slavery and human rights-related risks and opportunities.</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Annual progress reporting via the Modern Slavery Statement</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your area reported on the related SP2030 target 11c(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Annual Modern Slavery Statement, with case studies</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>We will draw on the annual Modern Slavery Statement and case studies to report on the University's approach to modern slavery and human rights risks (timing to be aligned with the Statement).</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>11c(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I19" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="J19" s="12" t="inlineStr">
         <is>
           <t>From Matt (20/1/26): Link to Annual Modern Slavery Statement; case study excerpt
 Link: https://modernslaveryregister.gov.au/statements/22714/
@@ -1026,312 +1009,314 @@
 In regard to what new information we are Ok with publishing on MS in regard to 2025 our approach is to collate this and have it approved for external consumption via this process.</t>
         </is>
       </c>
-      <c r="K19" s="14" t="inlineStr"/>
-      <c r="L19" s="15" t="n"/>
-      <c r="M19" s="15" t="n"/>
-      <c r="N19" s="15" t="n"/>
-      <c r="O19" s="15" t="n"/>
-      <c r="P19" s="15" t="n"/>
-      <c r="Q19" s="15" t="n"/>
+      <c r="K19" s="12" t="inlineStr"/>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="13" t="n"/>
+      <c r="N19" s="13" t="n"/>
+      <c r="O19" s="13" t="n"/>
+      <c r="P19" s="13" t="n"/>
+      <c r="Q19" s="13" t="n"/>
     </row>
     <row r="20" ht="150" customHeight="1">
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I20" s="14" t="inlineStr"/>
-      <c r="J20" s="14" t="inlineStr"/>
-      <c r="K20" s="14" t="inlineStr"/>
-      <c r="L20" s="15" t="n"/>
-      <c r="M20" s="15" t="n"/>
-      <c r="N20" s="15" t="n"/>
-      <c r="O20" s="15" t="n"/>
-      <c r="P20" s="15" t="n"/>
-      <c r="Q20" s="15" t="n"/>
+      <c r="I20" s="12" t="inlineStr"/>
+      <c r="J20" s="12" t="inlineStr"/>
+      <c r="K20" s="12" t="inlineStr"/>
+      <c r="L20" s="13" t="n"/>
+      <c r="M20" s="13" t="n"/>
+      <c r="N20" s="13" t="n"/>
+      <c r="O20" s="13" t="n"/>
+      <c r="P20" s="13" t="n"/>
+      <c r="Q20" s="13" t="n"/>
     </row>
     <row r="21" ht="150" customHeight="1">
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>EN1(d)</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Sustainability objectives integrated into governance and decision‑making processes, supported by transparent reporting.</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>Please provide evidence of how sustainability objectives are integrated into governance and decision-making within your Faculty/Portfolio, could include relevant committees, policies, planning or approval processes, accountability mechanisms and examples of transparent reporting.</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>We will report on how sustainability is integrated into governance and decision-making across faculties and portfolios, and use responses as a baseline for the governance enabler from 2027.</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr"/>
-      <c r="J21" s="14" t="inlineStr"/>
-      <c r="K21" s="14" t="inlineStr"/>
-      <c r="L21" s="15" t="n"/>
-      <c r="M21" s="15" t="n"/>
-      <c r="N21" s="15" t="n"/>
-      <c r="O21" s="15" t="n"/>
-      <c r="P21" s="15" t="n"/>
-      <c r="Q21" s="15" t="n"/>
+      <c r="I21" s="12" t="inlineStr"/>
+      <c r="J21" s="12" t="inlineStr"/>
+      <c r="K21" s="12" t="inlineStr"/>
+      <c r="L21" s="13" t="n"/>
+      <c r="M21" s="13" t="n"/>
+      <c r="N21" s="13" t="n"/>
+      <c r="O21" s="13" t="n"/>
+      <c r="P21" s="13" t="n"/>
+      <c r="Q21" s="13" t="n"/>
     </row>
     <row r="22"/>
-    <row r="24">
-      <c r="B24" s="6" t="inlineStr">
+    <row r="23"/>
+    <row r="24" ht="39" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>CFOG – Treasury &amp; Investments</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="C26" s="7" t="inlineStr">
+    <row r="25"/>
+    <row r="26" ht="27" customHeight="1">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L26" s="8" t="inlineStr">
+      <c r="L26" s="6" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="9" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L27" s="10" t="inlineStr">
+      <c r="L27" s="8" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M27" s="10" t="inlineStr">
+      <c r="M27" s="8" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N27" s="10" t="inlineStr">
+      <c r="N27" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O27" s="10" t="inlineStr">
+      <c r="O27" s="8" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P27" s="10" t="inlineStr">
+      <c r="P27" s="8" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q27" s="10" t="inlineStr">
+      <c r="Q27" s="8" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="11" t="inlineStr"/>
-      <c r="C28" s="11" t="inlineStr"/>
-      <c r="D28" s="11" t="inlineStr"/>
-      <c r="E28" s="11" t="inlineStr"/>
-      <c r="F28" s="11" t="inlineStr"/>
-      <c r="G28" s="11" t="inlineStr"/>
-      <c r="H28" s="11" t="inlineStr"/>
-      <c r="I28" s="11" t="inlineStr"/>
-      <c r="J28" s="11" t="inlineStr"/>
-      <c r="K28" s="11" t="inlineStr"/>
-      <c r="L28" s="11" t="inlineStr">
+    <row r="28" ht="81" customHeight="1">
+      <c r="B28" s="9" t="inlineStr"/>
+      <c r="C28" s="9" t="inlineStr"/>
+      <c r="D28" s="9" t="inlineStr"/>
+      <c r="E28" s="9" t="inlineStr"/>
+      <c r="F28" s="9" t="inlineStr"/>
+      <c r="G28" s="9" t="inlineStr"/>
+      <c r="H28" s="9" t="inlineStr"/>
+      <c r="I28" s="9" t="inlineStr"/>
+      <c r="J28" s="9" t="inlineStr"/>
+      <c r="K28" s="9" t="inlineStr"/>
+      <c r="L28" s="9" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M28" s="11" t="inlineStr">
+      <c r="M28" s="9" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N28" s="11" t="inlineStr">
+      <c r="N28" s="9" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O28" s="11" t="inlineStr">
+      <c r="O28" s="9" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P28" s="11" t="inlineStr">
+      <c r="P28" s="9" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q28" s="11" t="inlineStr">
+      <c r="Q28" s="9" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="150" customHeight="1">
-      <c r="B29" s="12" t="inlineStr">
+    <row r="29" ht="204" customHeight="1">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>Responsible investments</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Achieve net zero financed emissions for the University’s investment portfolio by 2050.</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Continuous improvement of the reporting of the University’s sustainability-related investment profile metrics, could include investment in climate mitigation and transition solutions, and compliance with related obligations (eg UNPRI).</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your area reported on the related SP2030 target 12b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Report on relevant sustainability-related investment portfolio metrics and report on how the University has complied with its related obligations
 Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>We will report on sustainability-related investment portfolio metrics and the University's compliance with related obligations (e.g. UNPRI) in the Responsible investments section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>12b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I29" s="14" t="inlineStr">
+      <c r="I29" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J29" s="14" t="inlineStr">
+      <c r="J29" s="12" t="inlineStr">
         <is>
           <t>Since 2022 the University has published its sustainability-related investment portfolio metrics including carbon intensity. Historically this has only applied to Australian &amp; International equities, but from this year we are able to also include Fixed Income &amp; Credit. Other asset classes will be included as the data relating to them becomes available and is considered reasonable. 
 While data and metrics are continuously being refined, we have met our target of enhanced transparent reporting of the investment portfolio.</t>
         </is>
       </c>
-      <c r="K29" s="14" t="inlineStr"/>
-      <c r="L29" s="15" t="n"/>
-      <c r="M29" s="15" t="n"/>
-      <c r="N29" s="15" t="n"/>
-      <c r="O29" s="15" t="n"/>
-      <c r="P29" s="15" t="n"/>
-      <c r="Q29" s="15" t="n"/>
+      <c r="K29" s="12" t="inlineStr"/>
+      <c r="L29" s="13" t="n"/>
+      <c r="M29" s="13" t="n"/>
+      <c r="N29" s="13" t="n"/>
+      <c r="O29" s="13" t="n"/>
+      <c r="P29" s="13" t="n"/>
+      <c r="Q29" s="13" t="n"/>
     </row>
     <row r="30"/>
   </sheetData>
@@ -1382,110 +1367,102 @@
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="17" t="inlineStr">
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
-    <row r="8">
-      <c r="B8" s="19" t="inlineStr">
+    <row r="7"/>
+    <row r="8" ht="39" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1516,136 +1493,125 @@
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>End-2025 target status assessment and reporting (for reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Your SR25 responses – Chief Finance Officer Group (CFOG)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="21" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="22" t="inlineStr">
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Procurement</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="9" t="inlineStr">
+    <row r="6" ht="42" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>The University has curated living labs covering the priority areas of this Plan</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Please describe any activities in Procurement which address sustainability issues via collaboration between academic and professional staff.</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr"/>
-      <c r="G7" s="14" t="inlineStr"/>
-      <c r="H7" s="14" t="inlineStr"/>
-      <c r="I7" s="14" t="inlineStr"/>
-    </row>
-    <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr"/>
+      <c r="G7" s="12" t="inlineStr"/>
+      <c r="H7" s="12" t="inlineStr"/>
+      <c r="I7" s="12" t="inlineStr"/>
+    </row>
+    <row r="8" ht="254" customHeight="1">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>11a(iii)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>The University has reduced waste to landfill to 10kg per person</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Case studies on end of life pathways for specialist university waste streams in 2025 (e.g. the lab equipment auction organised by Procurement c. 2023)</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Not provided (as agreed with Sustainability Strategy team)</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>From Jose:
 At the moment we do not track any reduction of waste in our operation. 
@@ -1655,62 +1621,62 @@
 In our space Tom Atta or Peter Sritharan would be able to confirm or guide internally who to talk to to confirm this initiative. The potential suppliers that are doing this are CompNow and/or Citadel or others in the AV Space.</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr"/>
-      <c r="H8" s="14" t="inlineStr"/>
-      <c r="I8" s="14" t="inlineStr"/>
+      <c r="G8" s="12" t="inlineStr"/>
+      <c r="H8" s="12" t="inlineStr"/>
+      <c r="I8" s="12" t="inlineStr"/>
     </row>
     <row r="9" ht="160" customHeight="1">
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>11b(iv)</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>The University has reduced the flow and improved the circularity of materials passing through the University</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Case studies demonstrating waste and/or circular economy innovation</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Not provided (as agreed with Sustainability Strategy team)</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>RH note: Not provided, but not critical for reporting.</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr"/>
-      <c r="H9" s="14" t="inlineStr"/>
-      <c r="I9" s="14" t="inlineStr"/>
+      <c r="G9" s="12" t="inlineStr"/>
+      <c r="H9" s="12" t="inlineStr"/>
+      <c r="I9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>11c(i)</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>The University has principles for ethical and sustainable consumption and service provision embedded into operations and procurement practices</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Link to Annual Modern Slavery Statement; case study excerpt</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>From Matt (20/1/26): Link to Annual Modern Slavery Statement; case study excerpt
 Link: https://modernslaveryregister.gov.au/statements/22714/
@@ -1718,101 +1684,101 @@
 In regard to what new information we are Ok with publishing on MS in regard to 2025 our approach is to collate this and have it approved for external consumption via this process.</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr"/>
-      <c r="H10" s="14" t="inlineStr"/>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr"/>
+      <c r="H10" s="12" t="inlineStr"/>
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>MS1(a)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="160" customHeight="1">
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>11c(ii)</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>The University has principles for ethical and sustainable consumption and service provision embedded into operations and procurement practices</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>List of Fair Trade and other relevant third-party certifications</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Not provided (as agreed with Sustainability Strategy team)</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>RH note: Not provided, but not critical for reporting</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr"/>
-      <c r="H11" s="14" t="inlineStr"/>
-      <c r="I11" s="14" t="inlineStr"/>
+      <c r="G11" s="12" t="inlineStr"/>
+      <c r="H11" s="12" t="inlineStr"/>
+      <c r="I11" s="12" t="inlineStr"/>
     </row>
     <row r="12" ht="160" customHeight="1">
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>11c(iii)</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>The University has principles for ethical and sustainable consumption and service provision embedded into operations and procurement practices</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Description of the process for integrating supplier code of conduct into procurement practices, and key outcomes from this process.</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>From Matt (20/1/26): This has not changed from prior years, are you able to use what we submitted last report? (RH note: Yes we can use this).
 From Matt (28/1/26): In 2025 we increased the University’s systemic approach e.g. embedding more outcome focus questions in tenders, enhancing Modern Slavery clauses, implementing a system approach to collecting subcontracted impact spend.</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr"/>
-      <c r="H12" s="14" t="inlineStr"/>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr"/>
+      <c r="H12" s="12" t="inlineStr"/>
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>RP1(a)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="160" customHeight="1">
-      <c r="B13" s="12" t="inlineStr">
+    <row r="13" ht="320" customHeight="1">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>11d</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>The University tracks spend with social and Indigenous suppliers, setting targets from 2024</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Dollars spent with suppliers that are classified as social and/or Indigenous supplies (for example, demonstrated by listings on Supply Nation, Social Traders etc) as a percentage of total spend</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>From Matt (20/1/26): As mentioned, due to integration issues with the ERP rollout we will only get direct spend data information at the end of this month (I don’t have an exact ETA yet).
 For the indirect spend (Indigenous/ Social impact suppliers hired via our primary suppliers) this is collated quarterly and Jase is planning on having the 2025 total figures in the next 3 weeks (the construction industry shuts down over Dec/Jan and so we have slower response times). 
@@ -1820,329 +1786,332 @@
 From Matt (28/1/26): What we need to get better at is getting closer to hitting our Indigenous and Social impact spend target (3% by 2030). We have recently created an Indigenous Procurement Working Group made up of key University decision makers to better enable progress in this area.</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr"/>
-      <c r="H13" s="14" t="inlineStr"/>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr"/>
+      <c r="H13" s="12" t="inlineStr"/>
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>RP2(a), RP2(b)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="22" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+    <row r="16" ht="42" customHeight="1">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="160" customHeight="1">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>8a(i)</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Assessment based on the Climate Change Preparedness Framework</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr"/>
-      <c r="G17" s="14" t="inlineStr"/>
-      <c r="H17" s="14" t="inlineStr"/>
-      <c r="I17" s="14" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr"/>
+      <c r="G17" s="12" t="inlineStr"/>
+      <c r="H17" s="12" t="inlineStr"/>
+      <c r="I17" s="12" t="inlineStr"/>
     </row>
     <row r="18" ht="160" customHeight="1">
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>8a(ii)</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Please provide commentary regarding the Portfolio/team's level of climate change preparedness. Refer to the Climate Change Preparedness Framework for guidance: https://www.unimelb.edu.au/sustainabilityreport/domain-3-walking-the-talk-in-our-operations/climate-resilience#progress-1</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr"/>
-      <c r="G18" s="14" t="inlineStr"/>
-      <c r="H18" s="14" t="inlineStr"/>
-      <c r="I18" s="14" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="22" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr"/>
+      <c r="G18" s="12" t="inlineStr"/>
+      <c r="H18" s="12" t="inlineStr"/>
+      <c r="I18" s="12" t="inlineStr"/>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>Treasury and Investments</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="9" t="inlineStr">
+    <row r="21" ht="42" customHeight="1">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="160" customHeight="1">
-      <c r="B22" s="12" t="inlineStr">
+    <row r="22" ht="188" customHeight="1">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>12b(i)</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Enhanced transparent reporting of the University’s investment portfolio</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Report on relevant sustainability-related investment portfolio metrics, including carbon intensity</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>Since 2022 the University has published its sustainability-related investment portfolio metrics including carbon intensity. Historically this has only applied to Australian &amp; International equities, but from this year we are able to also include Fixed Income &amp; Credit. Other asset classes will be included as the data relating to them becomes available and is considered reasonable. 
 While data and metrics are continuously being refined, we have met our target of enhanced transparent reporting of the investment portfolio.</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr"/>
-      <c r="H22" s="14" t="inlineStr"/>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr"/>
+      <c r="H22" s="12" t="inlineStr"/>
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="160" customHeight="1">
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>12b(ii)</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Enhanced transparent reporting of the University’s investment portfolio</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Reporting on how the University has complied with its related obligations</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>We have met the targets we set out to achieve in 2022 by being more transparent in our reporting.</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr"/>
-      <c r="H23" s="14" t="inlineStr"/>
-      <c r="I23" s="14" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="22" t="inlineStr">
+      <c r="G23" s="12" t="inlineStr"/>
+      <c r="H23" s="12" t="inlineStr"/>
+      <c r="I23" s="12" t="inlineStr"/>
+    </row>
+    <row r="24"/>
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Enterprise Portfolio and Investments</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="9" t="inlineStr">
+    <row r="26" ht="42" customHeight="1">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="160" customHeight="1">
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>8a(i)</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Assessment based on the Climate Change Preparedness Framework</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr"/>
-      <c r="G27" s="14" t="inlineStr"/>
-      <c r="H27" s="14" t="inlineStr"/>
-      <c r="I27" s="14" t="inlineStr"/>
+      <c r="F27" s="12" t="inlineStr"/>
+      <c r="G27" s="12" t="inlineStr"/>
+      <c r="H27" s="12" t="inlineStr"/>
+      <c r="I27" s="12" t="inlineStr"/>
     </row>
     <row r="28" ht="160" customHeight="1">
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>8a(ii)</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Please provide commentary regarding the Portfolio/team's level of climate change preparedness. Refer to the Climate Change Preparedness Framework for guidance: https://www.unimelb.edu.au/sustainabilityreport/domain-3-walking-the-talk-in-our-operations/climate-resilience#progress-1</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr"/>
-      <c r="G28" s="14" t="inlineStr"/>
-      <c r="H28" s="14" t="inlineStr"/>
-      <c r="I28" s="14" t="inlineStr"/>
+      <c r="F28" s="12" t="inlineStr"/>
+      <c r="G28" s="12" t="inlineStr"/>
+      <c r="H28" s="12" t="inlineStr"/>
+      <c r="I28" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2164,6 +2133,7 @@
   <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
@@ -2180,1351 +2150,1341 @@
     <col width="26" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>End-2026 target status assessment and reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Quantitative data – Chief Finance Officer Group (CFOG)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>These figures feed the Sustainability Databook (the University's authoritative quantitative source). Previous years are shown for context – please do not alter. Please provide the CY2026 value (provisional or year-to-date figures are fine; we will confirm final figures with you in January–February), the data source, and any change to definition or boundary. Due: Tuesday 15 December 2026.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="7" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="27" customHeight="1">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Context only (please do not alter)</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>Please fill in these cells</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="9" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>CY2023</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>CY2024</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>CY2025</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>CY2026 value</t>
         </is>
       </c>
-      <c r="L6" s="10" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t>Data source (file name, link or system)</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>Change to definition or boundary?</t>
         </is>
       </c>
-      <c r="N6" s="10" t="inlineStr">
+      <c r="N6" s="8" t="inlineStr">
         <is>
           <t>Notes / limitations</t>
         </is>
       </c>
-      <c r="O6" s="10" t="inlineStr">
+      <c r="O6" s="8" t="inlineStr">
         <is>
           <t>Useful case studies</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="23" t="inlineStr">
+    <row r="7" ht="46" customHeight="1">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>No instructions – context only.</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr"/>
-      <c r="D7" s="23" t="inlineStr"/>
-      <c r="E7" s="23" t="inlineStr"/>
-      <c r="F7" s="23" t="inlineStr"/>
-      <c r="G7" s="23" t="inlineStr"/>
-      <c r="H7" s="23" t="inlineStr"/>
-      <c r="I7" s="23" t="inlineStr"/>
-      <c r="J7" s="23" t="inlineStr"/>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>Please enter numerical values</t>
         </is>
       </c>
-      <c r="L7" s="23" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t>Please provide a file name or link to the data source</t>
         </is>
       </c>
-      <c r="M7" s="23" t="inlineStr">
+      <c r="M7" s="21" t="inlineStr">
         <is>
           <t>Describe any change since last year (or 'No change')</t>
         </is>
       </c>
-      <c r="N7" s="23" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>Please add any additional notes here</t>
         </is>
       </c>
-      <c r="O7" s="23" t="inlineStr">
+      <c r="O7" s="21" t="inlineStr">
         <is>
           <t>Please provide information on any useful case studies</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="12" t="inlineStr">
+    <row r="8" ht="39" customHeight="1">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>RP2(a)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>Percentage of Indigeneous spend of total addressable procurement spend</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Total procurement spending</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F8" s="24" t="n"/>
-      <c r="G8" s="24" t="n"/>
-      <c r="H8" s="24" t="n"/>
-      <c r="I8" s="24" t="n"/>
-      <c r="J8" s="14" t="inlineStr">
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K8" s="15" t="n"/>
-      <c r="L8" s="15" t="n"/>
-      <c r="M8" s="15" t="n"/>
-      <c r="N8" s="15" t="n"/>
-      <c r="O8" s="15" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="12" t="inlineStr">
+      <c r="K8" s="13" t="n"/>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="13" t="n"/>
+      <c r="O8" s="13" t="n"/>
+    </row>
+    <row r="9" ht="39" customHeight="1">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>RP2(a)</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr"/>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr"/>
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Total Indigeneous spending</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F9" s="24" t="n"/>
-      <c r="G9" s="24" t="n"/>
-      <c r="H9" s="24" t="n"/>
-      <c r="I9" s="24" t="n"/>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K9" s="14" t="n"/>
-      <c r="L9" s="14" t="n"/>
-      <c r="M9" s="14" t="n"/>
-      <c r="N9" s="14" t="n"/>
-      <c r="O9" s="14" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="12" t="inlineStr">
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="12" t="n"/>
+    </row>
+    <row r="10" ht="39" customHeight="1">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>RP2(a)</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr"/>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr"/>
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Percentage of Indigeneous spend of total addressable procurement spend</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F10" s="24" t="n"/>
-      <c r="G10" s="24" t="n"/>
-      <c r="H10" s="24" t="n"/>
-      <c r="I10" s="24" t="n"/>
-      <c r="J10" s="14" t="inlineStr">
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K10" s="14" t="n"/>
-      <c r="L10" s="14" t="n"/>
-      <c r="M10" s="14" t="n"/>
-      <c r="N10" s="14" t="n"/>
-      <c r="O10" s="14" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="12" t="inlineStr">
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="12" t="n"/>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="12" t="n"/>
+    </row>
+    <row r="11" ht="39" customHeight="1">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>RP2(b)</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Percentage of social spend of total addressable procurement spend</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Total procurement spending</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F11" s="24" t="n"/>
-      <c r="G11" s="24" t="n"/>
-      <c r="H11" s="24" t="n"/>
-      <c r="I11" s="24" t="n"/>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K11" s="15" t="n"/>
-      <c r="L11" s="15" t="n"/>
-      <c r="M11" s="15" t="n"/>
-      <c r="N11" s="15" t="n"/>
-      <c r="O11" s="15" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="12" t="inlineStr">
+      <c r="K11" s="13" t="n"/>
+      <c r="L11" s="13" t="n"/>
+      <c r="M11" s="13" t="n"/>
+      <c r="N11" s="13" t="n"/>
+      <c r="O11" s="13" t="n"/>
+    </row>
+    <row r="12" ht="39" customHeight="1">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>RP2(b)</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr"/>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr"/>
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Total social spending</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F12" s="24" t="n"/>
-      <c r="G12" s="24" t="n"/>
-      <c r="H12" s="24" t="n"/>
-      <c r="I12" s="24" t="n"/>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K12" s="14" t="n"/>
-      <c r="L12" s="14" t="n"/>
-      <c r="M12" s="14" t="n"/>
-      <c r="N12" s="14" t="n"/>
-      <c r="O12" s="14" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="12" t="inlineStr">
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="12" t="n"/>
+      <c r="M12" s="12" t="n"/>
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="12" t="n"/>
+    </row>
+    <row r="13" ht="39" customHeight="1">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>RP2(b)</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr"/>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr"/>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Percentage of Indigeneous spend of total addressable procurement spend</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F13" s="24" t="n"/>
-      <c r="G13" s="24" t="n"/>
-      <c r="H13" s="24" t="n"/>
-      <c r="I13" s="24" t="n"/>
-      <c r="J13" s="14" t="inlineStr">
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="22" t="n"/>
+      <c r="H13" s="22" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K13" s="14" t="n"/>
-      <c r="L13" s="14" t="n"/>
-      <c r="M13" s="14" t="n"/>
-      <c r="N13" s="14" t="n"/>
-      <c r="O13" s="14" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="12" t="inlineStr">
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="12" t="n"/>
+      <c r="M13" s="12" t="n"/>
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="12" t="n"/>
+    </row>
+    <row r="14" ht="105" customHeight="1">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>RI1(a)</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Annual monitoring and reporting on the investment portfolio's net zero transition progress, including tracking the percentage of AUM managed by investment managers aligned with (or commited to net zero by 2050</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Total Asset Under Management (AUM)</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F14" s="24" t="n"/>
-      <c r="G14" s="24" t="n"/>
-      <c r="H14" s="24" t="n"/>
-      <c r="I14" s="24" t="n"/>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K14" s="15" t="n"/>
-      <c r="L14" s="15" t="n"/>
-      <c r="M14" s="15" t="n"/>
-      <c r="N14" s="15" t="n"/>
-      <c r="O14" s="15" t="n"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="12" t="inlineStr">
+      <c r="K14" s="13" t="n"/>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="13" t="n"/>
+      <c r="N14" s="13" t="n"/>
+      <c r="O14" s="13" t="n"/>
+    </row>
+    <row r="15" ht="39" customHeight="1">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>RI1(a)</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr"/>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr"/>
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>AUM managed by Investment Managers aligned with net zero commitment</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F15" s="24" t="n"/>
-      <c r="G15" s="24" t="n"/>
-      <c r="H15" s="24" t="n"/>
-      <c r="I15" s="24" t="n"/>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="22" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K15" s="14" t="n"/>
-      <c r="L15" s="14" t="n"/>
-      <c r="M15" s="14" t="n"/>
-      <c r="N15" s="14" t="n"/>
-      <c r="O15" s="14" t="n"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="12" t="inlineStr">
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="12" t="n"/>
+      <c r="N15" s="12" t="n"/>
+      <c r="O15" s="12" t="n"/>
+    </row>
+    <row r="16" ht="39" customHeight="1">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>RI1(a)</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr"/>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr"/>
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Percentage of AUM managed by Investment Managers aligned with net zero commitment</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F16" s="24" t="n"/>
-      <c r="G16" s="24" t="n"/>
-      <c r="H16" s="24" t="n"/>
-      <c r="I16" s="24" t="n"/>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="F16" s="22" t="n"/>
+      <c r="G16" s="22" t="n"/>
+      <c r="H16" s="22" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K16" s="14" t="n"/>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="14" t="n"/>
-      <c r="N16" s="14" t="n"/>
-      <c r="O16" s="14" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="12" t="n"/>
+      <c r="N16" s="12" t="n"/>
+      <c r="O16" s="12" t="n"/>
+    </row>
+    <row r="17" ht="122" customHeight="1">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Continuous improvement of the reporting of the University's sustainability-related investment profile metrics, including investment in climate mitigation and transition solutions, and compliance with related obligations (e.g. UNPRI)</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Total Asset Under Management (AUM)</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F17" s="24" t="n"/>
-      <c r="G17" s="24" t="n"/>
-      <c r="H17" s="24" t="n"/>
-      <c r="I17" s="24" t="n"/>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="22" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K17" s="15" t="n"/>
-      <c r="L17" s="15" t="n"/>
-      <c r="M17" s="15" t="n"/>
-      <c r="N17" s="15" t="n"/>
-      <c r="O17" s="15" t="n"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="12" t="inlineStr">
+      <c r="K17" s="13" t="n"/>
+      <c r="L17" s="13" t="n"/>
+      <c r="M17" s="13" t="n"/>
+      <c r="N17" s="13" t="n"/>
+      <c r="O17" s="13" t="n"/>
+    </row>
+    <row r="18" ht="39" customHeight="1">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr"/>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr"/>
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>AUM invested in climate/transition solution</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F18" s="24" t="n"/>
-      <c r="G18" s="24" t="n"/>
-      <c r="H18" s="24" t="n"/>
-      <c r="I18" s="24" t="n"/>
-      <c r="J18" s="14" t="inlineStr">
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="22" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K18" s="14" t="n"/>
-      <c r="L18" s="14" t="n"/>
-      <c r="M18" s="14" t="n"/>
-      <c r="N18" s="14" t="n"/>
-      <c r="O18" s="14" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="12" t="inlineStr">
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="12" t="n"/>
+      <c r="M18" s="12" t="n"/>
+      <c r="N18" s="12" t="n"/>
+      <c r="O18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="39" customHeight="1">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr"/>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr"/>
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Percentage of AUM invested in climate/transition solution</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F19" s="24" t="n"/>
-      <c r="G19" s="24" t="n"/>
-      <c r="H19" s="24" t="n"/>
-      <c r="I19" s="24" t="n"/>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="F19" s="22" t="n"/>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K19" s="14" t="n"/>
-      <c r="L19" s="14" t="n"/>
-      <c r="M19" s="14" t="n"/>
-      <c r="N19" s="14" t="n"/>
-      <c r="O19" s="14" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="12" t="inlineStr">
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="12" t="n"/>
+      <c r="O19" s="12" t="n"/>
+    </row>
+    <row r="20" ht="39" customHeight="1">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr"/>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr"/>
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Estimated UoM absolute financed carbon emissions</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F20" s="24" t="n"/>
-      <c r="G20" s="24" t="n">
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="22" t="n">
         <v>121733</v>
       </c>
-      <c r="H20" s="24" t="n">
+      <c r="H20" s="22" t="n">
         <v>111919</v>
       </c>
-      <c r="I20" s="24" t="n">
+      <c r="I20" s="22" t="n">
         <v>123381</v>
       </c>
-      <c r="J20" s="14" t="inlineStr">
+      <c r="J20" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K20" s="14" t="n"/>
-      <c r="L20" s="14" t="n"/>
-      <c r="M20" s="14" t="n"/>
-      <c r="N20" s="14" t="n"/>
-      <c r="O20" s="14" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="12" t="inlineStr">
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="12" t="n"/>
+      <c r="N20" s="12" t="n"/>
+      <c r="O20" s="12" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr"/>
-      <c r="D21" s="25" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr"/>
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>Australian Equities</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F21" s="24" t="n"/>
-      <c r="G21" s="24" t="n">
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="22" t="n">
         <v>101663</v>
       </c>
-      <c r="H21" s="24" t="n">
+      <c r="H21" s="22" t="n">
         <v>82052</v>
       </c>
-      <c r="I21" s="24" t="n">
+      <c r="I21" s="22" t="n">
         <v>57483</v>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="J21" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K21" s="14" t="n"/>
-      <c r="L21" s="14" t="n"/>
-      <c r="M21" s="14" t="n"/>
-      <c r="N21" s="14" t="n"/>
-      <c r="O21" s="14" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="12" t="inlineStr">
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="12" t="n"/>
+      <c r="N21" s="12" t="n"/>
+      <c r="O21" s="12" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr"/>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr"/>
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>International Equities</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F22" s="24" t="n"/>
-      <c r="G22" s="24" t="n">
+      <c r="F22" s="22" t="n"/>
+      <c r="G22" s="22" t="n">
         <v>20070</v>
       </c>
-      <c r="H22" s="24" t="n">
+      <c r="H22" s="22" t="n">
         <v>29867</v>
       </c>
-      <c r="I22" s="24" t="n">
+      <c r="I22" s="22" t="n">
         <v>27910</v>
       </c>
-      <c r="J22" s="14" t="inlineStr">
+      <c r="J22" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K22" s="14" t="n"/>
-      <c r="L22" s="14" t="n"/>
-      <c r="M22" s="14" t="n"/>
-      <c r="N22" s="14" t="n"/>
-      <c r="O22" s="14" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="12" t="inlineStr">
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="12" t="n"/>
+      <c r="N22" s="12" t="n"/>
+      <c r="O22" s="12" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr"/>
-      <c r="D23" s="25" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr"/>
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F23" s="24" t="n"/>
-      <c r="G23" s="24" t="inlineStr">
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H23" s="24" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I23" s="24" t="n">
+      <c r="I23" s="22" t="n">
         <v>9312</v>
       </c>
-      <c r="J23" s="14" t="inlineStr">
+      <c r="J23" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K23" s="14" t="n"/>
-      <c r="L23" s="14" t="n"/>
-      <c r="M23" s="14" t="n"/>
-      <c r="N23" s="14" t="n"/>
-      <c r="O23" s="14" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="12" t="inlineStr">
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
+      <c r="N23" s="12" t="n"/>
+      <c r="O23" s="12" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr"/>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr"/>
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>Fixed Interest</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F24" s="24" t="n"/>
-      <c r="G24" s="24" t="inlineStr">
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H24" s="24" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I24" s="24" t="n">
+      <c r="I24" s="22" t="n">
         <v>28676</v>
       </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="J24" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K24" s="14" t="n"/>
-      <c r="L24" s="14" t="n"/>
-      <c r="M24" s="14" t="n"/>
-      <c r="N24" s="14" t="n"/>
-      <c r="O24" s="14" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="12" t="inlineStr">
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+      <c r="N24" s="12" t="n"/>
+      <c r="O24" s="12" t="n"/>
+    </row>
+    <row r="25" ht="39" customHeight="1">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr"/>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr"/>
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>Estimated UoM absolute financed carbon emissions intensity</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F25" s="24" t="n"/>
-      <c r="G25" s="24" t="n">
+      <c r="F25" s="22" t="n"/>
+      <c r="G25" s="22" t="n">
         <v>55</v>
       </c>
-      <c r="H25" s="24" t="n">
+      <c r="H25" s="22" t="n">
         <v>49</v>
       </c>
-      <c r="I25" s="24" t="n">
+      <c r="I25" s="22" t="n">
         <v>38.2</v>
       </c>
-      <c r="J25" s="14" t="inlineStr">
+      <c r="J25" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K25" s="14" t="n"/>
-      <c r="L25" s="14" t="n"/>
-      <c r="M25" s="14" t="n"/>
-      <c r="N25" s="14" t="n"/>
-      <c r="O25" s="14" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="12" t="inlineStr">
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+      <c r="N25" s="12" t="n"/>
+      <c r="O25" s="12" t="n"/>
+    </row>
+    <row r="26" ht="39" customHeight="1">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr"/>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr"/>
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>Australian Equities</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F26" s="24" t="n"/>
-      <c r="G26" s="24" t="n">
+      <c r="F26" s="22" t="n"/>
+      <c r="G26" s="22" t="n">
         <v>94</v>
       </c>
-      <c r="H26" s="24" t="n">
+      <c r="H26" s="22" t="n">
         <v>72</v>
       </c>
-      <c r="I26" s="24" t="n">
+      <c r="I26" s="22" t="n">
         <v>52.6</v>
       </c>
-      <c r="J26" s="14" t="inlineStr">
+      <c r="J26" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K26" s="14" t="n"/>
-      <c r="L26" s="14" t="n"/>
-      <c r="M26" s="14" t="n"/>
-      <c r="N26" s="14" t="n"/>
-      <c r="O26" s="14" t="n"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="12" t="inlineStr">
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+      <c r="N26" s="12" t="n"/>
+      <c r="O26" s="12" t="n"/>
+    </row>
+    <row r="27" ht="39" customHeight="1">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr"/>
-      <c r="D27" s="25" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr"/>
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>International Equities</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F27" s="24" t="n"/>
-      <c r="G27" s="24" t="n">
+      <c r="F27" s="22" t="n"/>
+      <c r="G27" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="H27" s="24" t="n">
+      <c r="H27" s="22" t="n">
         <v>26</v>
       </c>
-      <c r="I27" s="24" t="n">
+      <c r="I27" s="22" t="n">
         <v>23.4</v>
       </c>
-      <c r="J27" s="14" t="inlineStr">
+      <c r="J27" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K27" s="14" t="n"/>
-      <c r="L27" s="14" t="n"/>
-      <c r="M27" s="14" t="n"/>
-      <c r="N27" s="14" t="n"/>
-      <c r="O27" s="14" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="12" t="inlineStr">
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+      <c r="N27" s="12" t="n"/>
+      <c r="O27" s="12" t="n"/>
+    </row>
+    <row r="28" ht="39" customHeight="1">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr"/>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr"/>
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F28" s="24" t="n"/>
-      <c r="G28" s="24" t="inlineStr">
+      <c r="F28" s="22" t="n"/>
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H28" s="24" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I28" s="24" t="n">
+      <c r="I28" s="22" t="n">
         <v>43.1</v>
       </c>
-      <c r="J28" s="14" t="inlineStr">
+      <c r="J28" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K28" s="14" t="n"/>
-      <c r="L28" s="14" t="n"/>
-      <c r="M28" s="14" t="n"/>
-      <c r="N28" s="14" t="n"/>
-      <c r="O28" s="14" t="n"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="12" t="inlineStr">
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="12" t="n"/>
+      <c r="N28" s="12" t="n"/>
+      <c r="O28" s="12" t="n"/>
+    </row>
+    <row r="29" ht="39" customHeight="1">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr"/>
-      <c r="D29" s="25" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr"/>
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>Fixed Interest</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F29" s="24" t="n"/>
-      <c r="G29" s="24" t="inlineStr">
+      <c r="F29" s="22" t="n"/>
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H29" s="24" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I29" s="24" t="n">
+      <c r="I29" s="22" t="n">
         <v>54.3</v>
       </c>
-      <c r="J29" s="14" t="inlineStr">
+      <c r="J29" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K29" s="14" t="n"/>
-      <c r="L29" s="14" t="n"/>
-      <c r="M29" s="14" t="n"/>
-      <c r="N29" s="14" t="n"/>
-      <c r="O29" s="14" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="12" t="inlineStr">
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+      <c r="N29" s="12" t="n"/>
+      <c r="O29" s="12" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr"/>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr"/>
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>Benchmark financed carbon emissions</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F30" s="24" t="n"/>
-      <c r="G30" s="24" t="n">
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="22" t="n">
         <v>103250</v>
       </c>
-      <c r="H30" s="24" t="n">
+      <c r="H30" s="22" t="n">
         <v>118609</v>
       </c>
-      <c r="I30" s="24" t="n">
+      <c r="I30" s="22" t="n">
         <v>143399</v>
       </c>
-      <c r="J30" s="14" t="inlineStr">
+      <c r="J30" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K30" s="14" t="n"/>
-      <c r="L30" s="14" t="n"/>
-      <c r="M30" s="14" t="n"/>
-      <c r="N30" s="14" t="n"/>
-      <c r="O30" s="14" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="12" t="inlineStr">
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+      <c r="N30" s="12" t="n"/>
+      <c r="O30" s="12" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr"/>
-      <c r="D31" s="25" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr"/>
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>Australian Equities</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F31" s="24" t="n"/>
-      <c r="G31" s="24" t="n">
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="22" t="n">
         <v>62433</v>
       </c>
-      <c r="H31" s="24" t="n">
+      <c r="H31" s="22" t="n">
         <v>76031</v>
       </c>
-      <c r="I31" s="24" t="n">
+      <c r="I31" s="22" t="n">
         <v>49827</v>
       </c>
-      <c r="J31" s="14" t="inlineStr">
+      <c r="J31" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K31" s="14" t="n"/>
-      <c r="L31" s="14" t="n"/>
-      <c r="M31" s="14" t="n"/>
-      <c r="N31" s="14" t="n"/>
-      <c r="O31" s="14" t="n"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="12" t="inlineStr">
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12" t="n"/>
+      <c r="N31" s="12" t="n"/>
+      <c r="O31" s="12" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr"/>
-      <c r="D32" s="25" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr"/>
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>International Equities</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F32" s="24" t="n"/>
-      <c r="G32" s="24" t="n">
+      <c r="F32" s="22" t="n"/>
+      <c r="G32" s="22" t="n">
         <v>40817</v>
       </c>
-      <c r="H32" s="24" t="n">
+      <c r="H32" s="22" t="n">
         <v>42578</v>
       </c>
-      <c r="I32" s="24" t="n">
+      <c r="I32" s="22" t="n">
         <v>34989</v>
       </c>
-      <c r="J32" s="14" t="inlineStr">
+      <c r="J32" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K32" s="14" t="n"/>
-      <c r="L32" s="14" t="n"/>
-      <c r="M32" s="14" t="n"/>
-      <c r="N32" s="14" t="n"/>
-      <c r="O32" s="14" t="n"/>
-    </row>
-    <row r="33">
-      <c r="B33" s="12" t="inlineStr">
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="12" t="n"/>
+    </row>
+    <row r="33" ht="39" customHeight="1">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr"/>
-      <c r="D33" s="25" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr"/>
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F33" s="24" t="n"/>
-      <c r="G33" s="24" t="inlineStr">
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H33" s="24" t="inlineStr">
+      <c r="H33" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I33" s="24" t="inlineStr">
+      <c r="I33" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J33" s="14" t="inlineStr">
+      <c r="J33" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K33" s="14" t="n"/>
-      <c r="L33" s="14" t="n"/>
-      <c r="M33" s="14" t="n"/>
-      <c r="N33" s="14" t="n"/>
-      <c r="O33" s="14" t="n"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="12" t="inlineStr">
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="12" t="n"/>
+      <c r="N33" s="12" t="n"/>
+      <c r="O33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr"/>
-      <c r="D34" s="25" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr"/>
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>Fixed Interest</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F34" s="24" t="n"/>
-      <c r="G34" s="24" t="inlineStr">
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H34" s="24" t="inlineStr">
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I34" s="24" t="n">
+      <c r="I34" s="22" t="n">
         <v>58583</v>
       </c>
-      <c r="J34" s="14" t="inlineStr">
+      <c r="J34" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K34" s="14" t="n"/>
-      <c r="L34" s="14" t="n"/>
-      <c r="M34" s="14" t="n"/>
-      <c r="N34" s="14" t="n"/>
-      <c r="O34" s="14" t="n"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="12" t="inlineStr">
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="12" t="n"/>
+      <c r="N34" s="12" t="n"/>
+      <c r="O34" s="12" t="n"/>
+    </row>
+    <row r="35" ht="39" customHeight="1">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr"/>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr"/>
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>Benchmark financed carbon emissions intensity</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F35" s="24" t="n"/>
-      <c r="G35" s="24" t="n">
+      <c r="F35" s="22" t="n"/>
+      <c r="G35" s="22" t="n">
         <v>47</v>
       </c>
-      <c r="H35" s="24" t="n">
+      <c r="H35" s="22" t="n">
         <v>51</v>
       </c>
-      <c r="I35" s="24" t="n">
+      <c r="I35" s="22" t="n">
         <v>48.6</v>
       </c>
-      <c r="J35" s="14" t="inlineStr">
+      <c r="J35" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K35" s="14" t="n"/>
-      <c r="L35" s="14" t="n"/>
-      <c r="M35" s="14" t="n"/>
-      <c r="N35" s="14" t="n"/>
-      <c r="O35" s="14" t="n"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="12" t="inlineStr">
+      <c r="K35" s="12" t="n"/>
+      <c r="L35" s="12" t="n"/>
+      <c r="M35" s="12" t="n"/>
+      <c r="N35" s="12" t="n"/>
+      <c r="O35" s="12" t="n"/>
+    </row>
+    <row r="36" ht="39" customHeight="1">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr"/>
-      <c r="D36" s="25" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr"/>
+      <c r="D36" s="23" t="inlineStr">
         <is>
           <t>Australian Equities</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F36" s="24" t="n"/>
-      <c r="G36" s="24" t="n">
+      <c r="F36" s="22" t="n"/>
+      <c r="G36" s="22" t="n">
         <v>58</v>
       </c>
-      <c r="H36" s="24" t="n">
+      <c r="H36" s="22" t="n">
         <v>67</v>
       </c>
-      <c r="I36" s="24" t="n">
+      <c r="I36" s="22" t="n">
         <v>45.6</v>
       </c>
-      <c r="J36" s="14" t="inlineStr">
+      <c r="J36" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K36" s="14" t="n"/>
-      <c r="L36" s="14" t="n"/>
-      <c r="M36" s="14" t="n"/>
-      <c r="N36" s="14" t="n"/>
-      <c r="O36" s="14" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="12" t="inlineStr">
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="12" t="n"/>
+      <c r="N36" s="12" t="n"/>
+      <c r="O36" s="12" t="n"/>
+    </row>
+    <row r="37" ht="39" customHeight="1">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr"/>
-      <c r="D37" s="25" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr"/>
+      <c r="D37" s="23" t="inlineStr">
         <is>
           <t>International Equities</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F37" s="24" t="n"/>
-      <c r="G37" s="24" t="n">
+      <c r="F37" s="22" t="n"/>
+      <c r="G37" s="22" t="n">
         <v>36</v>
       </c>
-      <c r="H37" s="24" t="n">
+      <c r="H37" s="22" t="n">
         <v>37</v>
       </c>
-      <c r="I37" s="24" t="n">
+      <c r="I37" s="22" t="n">
         <v>26</v>
       </c>
-      <c r="J37" s="14" t="inlineStr">
+      <c r="J37" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K37" s="14" t="n"/>
-      <c r="L37" s="14" t="n"/>
-      <c r="M37" s="14" t="n"/>
-      <c r="N37" s="14" t="n"/>
-      <c r="O37" s="14" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="12" t="inlineStr">
+      <c r="K37" s="12" t="n"/>
+      <c r="L37" s="12" t="n"/>
+      <c r="M37" s="12" t="n"/>
+      <c r="N37" s="12" t="n"/>
+      <c r="O37" s="12" t="n"/>
+    </row>
+    <row r="38" ht="39" customHeight="1">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr"/>
-      <c r="D38" s="25" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr"/>
+      <c r="D38" s="23" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F38" s="24" t="n"/>
-      <c r="G38" s="24" t="inlineStr">
+      <c r="F38" s="22" t="n"/>
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H38" s="24" t="inlineStr">
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I38" s="24" t="inlineStr">
+      <c r="I38" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J38" s="14" t="inlineStr">
+      <c r="J38" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K38" s="14" t="n"/>
-      <c r="L38" s="14" t="n"/>
-      <c r="M38" s="14" t="n"/>
-      <c r="N38" s="14" t="n"/>
-      <c r="O38" s="14" t="n"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="12" t="inlineStr">
+      <c r="K38" s="12" t="n"/>
+      <c r="L38" s="12" t="n"/>
+      <c r="M38" s="12" t="n"/>
+      <c r="N38" s="12" t="n"/>
+      <c r="O38" s="12" t="n"/>
+    </row>
+    <row r="39" ht="39" customHeight="1">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C39" s="14" t="inlineStr"/>
-      <c r="D39" s="25" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr"/>
+      <c r="D39" s="23" t="inlineStr">
         <is>
           <t>Fixed Interest</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F39" s="24" t="n"/>
-      <c r="G39" s="24" t="inlineStr">
+      <c r="F39" s="22" t="n"/>
+      <c r="G39" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H39" s="24" t="inlineStr">
+      <c r="H39" s="22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I39" s="24" t="n">
+      <c r="I39" s="22" t="n">
         <v>112.9</v>
       </c>
-      <c r="J39" s="14" t="inlineStr">
+      <c r="J39" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K39" s="14" t="n"/>
-      <c r="L39" s="14" t="n"/>
-      <c r="M39" s="14" t="n"/>
-      <c r="N39" s="14" t="n"/>
-      <c r="O39" s="14" t="n"/>
+      <c r="K39" s="12" t="n"/>
+      <c r="L39" s="12" t="n"/>
+      <c r="M39" s="12" t="n"/>
+      <c r="N39" s="12" t="n"/>
+      <c r="O39" s="12" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -3548,10 +3508,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="B1" t="inlineStr">
         <is>
           <t>(not used – no target status rating in 2026)</t>
@@ -3573,7 +3540,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="22" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
           <t>Please select from dropdown</t>
@@ -3595,7 +3562,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -3612,7 +3579,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="22" customHeight="1">
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -3629,35 +3596,35 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="D8" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="D9" t="inlineStr">
         <is>
           <t>Not required</t>

--- a/output/central_unit_requests/CFOG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CFOG - SR26 sustainability reporting request.xlsx
@@ -650,7 +650,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/CFOG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CFOG - SR26 sustainability reporting request.xlsx
@@ -34,7 +34,7 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00002060"/>
+      <color rgb="00FFFFFF"/>
       <sz val="22"/>
     </font>
     <font>
@@ -118,7 +118,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -143,6 +143,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C1E4F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00000F46"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,9 +183,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="4"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -314,6 +322,126 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -605,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:R30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -625,24 +753,61 @@
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -650,7 +815,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Thursday 24 December 2026 (Christmas shutdown). Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>
@@ -661,7 +826,7 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11" ht="39" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>CFOG – Procurement</t>
         </is>
@@ -669,339 +834,339 @@
     </row>
     <row r="12"/>
     <row r="13" ht="27" customHeight="1">
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="P14" s="9" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="Q14" s="9" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="81" customHeight="1">
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="9" t="inlineStr"/>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr"/>
-      <c r="J15" s="9" t="inlineStr"/>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="9" t="inlineStr">
+      <c r="O15" s="10" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="9" t="inlineStr">
+      <c r="P15" s="10" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="9" t="inlineStr">
+      <c r="Q15" s="10" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>TR3(b)</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>Please describe any efforts within your Faculty/Portfolio to make research practices more sustainable, could include examples from laboratories, fieldwork, procurement, research travel or infrastructure use. Where available, provide evidence of uptake, resource savings, emissions reductions or other outcomes.</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr"/>
-      <c r="J16" s="12" t="inlineStr"/>
-      <c r="K16" s="12" t="inlineStr"/>
-      <c r="L16" s="13" t="n"/>
-      <c r="M16" s="13" t="n"/>
-      <c r="N16" s="13" t="n"/>
-      <c r="O16" s="13" t="n"/>
-      <c r="P16" s="13" t="n"/>
-      <c r="Q16" s="13" t="n"/>
+      <c r="I16" s="13" t="inlineStr"/>
+      <c r="J16" s="13" t="inlineStr"/>
+      <c r="K16" s="13" t="inlineStr"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n"/>
+      <c r="P16" s="14" t="n"/>
+      <c r="Q16" s="14" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>NB2(c)</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Nature and biodiversity</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Improve our understanding of our supply chain impacts on nature.</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Evidence of prioritised high risk procurement categories or suppliers for nature impact management</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Please provide the prioritised high-risk procurement categories and/or suppliers identified for nature-impact management, could include the basis for prioritisation and any risk-management, engagement or mitigation actions undertaken or planned.</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>We will report on the high-risk procurement categories or suppliers prioritised for nature-impact management, and related actions, in the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr"/>
-      <c r="K17" s="12" t="inlineStr"/>
-      <c r="L17" s="13" t="n"/>
-      <c r="M17" s="13" t="n"/>
-      <c r="N17" s="13" t="n"/>
-      <c r="O17" s="13" t="n"/>
-      <c r="P17" s="13" t="n"/>
-      <c r="Q17" s="13" t="n"/>
+      <c r="I17" s="13" t="inlineStr"/>
+      <c r="J17" s="13" t="inlineStr"/>
+      <c r="K17" s="13" t="inlineStr"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="14" t="n"/>
+      <c r="P17" s="14" t="n"/>
+      <c r="Q17" s="14" t="n"/>
     </row>
     <row r="18" ht="150" customHeight="1">
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>RP1(a)</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Responsible procurement</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Strengthen our ethical and sustainable procurement approach.</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Case studies of maturity improvement related to responsible procurement process and systems.</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 11c(iii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Maturity score if framework established; % procurement staff trained</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>Maturity score if framework established; % procurement staff trained
+In end-2025 reporting your area reported on the related SP2030 target 11c(iii) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>We will use case studies (and any maturity score or training data) to show improvement in responsible procurement processes and systems in the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>11c(iii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I18" s="12" t="inlineStr">
+      <c r="I18" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>From Matt (20/1/26): This has not changed from prior years, are you able to use what we submitted last report? (RH note: Yes we can use this).
 From Matt (28/1/26): In 2025 we increased the University’s systemic approach e.g. embedding more outcome focus questions in tenders, enhancing Modern Slavery clauses, implementing a system approach to collecting subcontracted impact spend.</t>
         </is>
       </c>
-      <c r="K18" s="12" t="inlineStr"/>
-      <c r="L18" s="13" t="n"/>
-      <c r="M18" s="13" t="n"/>
-      <c r="N18" s="13" t="n"/>
-      <c r="O18" s="13" t="n"/>
-      <c r="P18" s="13" t="n"/>
-      <c r="Q18" s="13" t="n"/>
+      <c r="K18" s="13" t="inlineStr"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
+      <c r="N18" s="14" t="n"/>
+      <c r="O18" s="14" t="n"/>
+      <c r="P18" s="14" t="n"/>
+      <c r="Q18" s="14" t="n"/>
     </row>
     <row r="19" ht="150" customHeight="1">
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>MS1(a)</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>Modern slavery and human rights</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Manage our approach to modern slavery and human rights-related risks and opportunities.</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Annual progress reporting via the Modern Slavery Statement</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 11c(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Annual Modern Slavery Statement, with case studies</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Annual Modern Slavery Statement, with case studies
+In end-2025 reporting your area reported on the related SP2030 target 11c(i) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>We will draw on the annual Modern Slavery Statement and case studies to report on the University's approach to modern slavery and human rights risks (timing to be aligned with the Statement).</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr">
         <is>
           <t>11c(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I19" s="12" t="inlineStr">
+      <c r="I19" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J19" s="12" t="inlineStr">
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>From Matt (20/1/26): Link to Annual Modern Slavery Statement; case study excerpt
 Link: https://modernslaveryregister.gov.au/statements/22714/
@@ -1009,110 +1174,110 @@
 In regard to what new information we are Ok with publishing on MS in regard to 2025 our approach is to collate this and have it approved for external consumption via this process.</t>
         </is>
       </c>
-      <c r="K19" s="12" t="inlineStr"/>
-      <c r="L19" s="13" t="n"/>
-      <c r="M19" s="13" t="n"/>
-      <c r="N19" s="13" t="n"/>
-      <c r="O19" s="13" t="n"/>
-      <c r="P19" s="13" t="n"/>
-      <c r="Q19" s="13" t="n"/>
+      <c r="K19" s="13" t="inlineStr"/>
+      <c r="L19" s="14" t="n"/>
+      <c r="M19" s="14" t="n"/>
+      <c r="N19" s="14" t="n"/>
+      <c r="O19" s="14" t="n"/>
+      <c r="P19" s="14" t="n"/>
+      <c r="Q19" s="14" t="n"/>
     </row>
     <row r="20" ht="150" customHeight="1">
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H20" s="13" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I20" s="12" t="inlineStr"/>
-      <c r="J20" s="12" t="inlineStr"/>
-      <c r="K20" s="12" t="inlineStr"/>
-      <c r="L20" s="13" t="n"/>
-      <c r="M20" s="13" t="n"/>
-      <c r="N20" s="13" t="n"/>
-      <c r="O20" s="13" t="n"/>
-      <c r="P20" s="13" t="n"/>
-      <c r="Q20" s="13" t="n"/>
+      <c r="I20" s="13" t="inlineStr"/>
+      <c r="J20" s="13" t="inlineStr"/>
+      <c r="K20" s="13" t="inlineStr"/>
+      <c r="L20" s="14" t="n"/>
+      <c r="M20" s="14" t="n"/>
+      <c r="N20" s="14" t="n"/>
+      <c r="O20" s="14" t="n"/>
+      <c r="P20" s="14" t="n"/>
+      <c r="Q20" s="14" t="n"/>
     </row>
     <row r="21" ht="150" customHeight="1">
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>EN1(d)</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Sustainability objectives integrated into governance and decision‑making processes, supported by transparent reporting.</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>Please provide evidence of how sustainability objectives are integrated into governance and decision-making within your Faculty/Portfolio, could include relevant committees, policies, planning or approval processes, accountability mechanisms and examples of transparent reporting.</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>We will report on how sustainability is integrated into governance and decision-making across faculties and portfolios, and use responses as a baseline for the governance enabler from 2027.</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr">
+      <c r="H21" s="13" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr"/>
-      <c r="J21" s="12" t="inlineStr"/>
-      <c r="K21" s="12" t="inlineStr"/>
-      <c r="L21" s="13" t="n"/>
-      <c r="M21" s="13" t="n"/>
-      <c r="N21" s="13" t="n"/>
-      <c r="O21" s="13" t="n"/>
-      <c r="P21" s="13" t="n"/>
-      <c r="Q21" s="13" t="n"/>
+      <c r="I21" s="13" t="inlineStr"/>
+      <c r="J21" s="13" t="inlineStr"/>
+      <c r="K21" s="13" t="inlineStr"/>
+      <c r="L21" s="14" t="n"/>
+      <c r="M21" s="14" t="n"/>
+      <c r="N21" s="14" t="n"/>
+      <c r="O21" s="14" t="n"/>
+      <c r="P21" s="14" t="n"/>
+      <c r="Q21" s="14" t="n"/>
     </row>
     <row r="22"/>
     <row r="23"/>
     <row r="24" ht="39" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>CFOG – Treasury &amp; Investments</t>
         </is>
@@ -1120,203 +1285,203 @@
     </row>
     <row r="25"/>
     <row r="26" ht="27" customHeight="1">
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L26" s="6" t="inlineStr">
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="60" customHeight="1">
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr">
+      <c r="K27" s="8" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M27" s="8" t="inlineStr">
+      <c r="M27" s="9" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr">
+      <c r="N27" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
+      <c r="O27" s="9" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P27" s="8" t="inlineStr">
+      <c r="P27" s="9" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q27" s="8" t="inlineStr">
+      <c r="Q27" s="9" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="81" customHeight="1">
-      <c r="B28" s="9" t="inlineStr"/>
-      <c r="C28" s="9" t="inlineStr"/>
-      <c r="D28" s="9" t="inlineStr"/>
-      <c r="E28" s="9" t="inlineStr"/>
-      <c r="F28" s="9" t="inlineStr"/>
-      <c r="G28" s="9" t="inlineStr"/>
-      <c r="H28" s="9" t="inlineStr"/>
-      <c r="I28" s="9" t="inlineStr"/>
-      <c r="J28" s="9" t="inlineStr"/>
-      <c r="K28" s="9" t="inlineStr"/>
-      <c r="L28" s="9" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr"/>
+      <c r="C28" s="10" t="inlineStr"/>
+      <c r="D28" s="10" t="inlineStr"/>
+      <c r="E28" s="10" t="inlineStr"/>
+      <c r="F28" s="10" t="inlineStr"/>
+      <c r="G28" s="10" t="inlineStr"/>
+      <c r="H28" s="10" t="inlineStr"/>
+      <c r="I28" s="10" t="inlineStr"/>
+      <c r="J28" s="10" t="inlineStr"/>
+      <c r="K28" s="10" t="inlineStr"/>
+      <c r="L28" s="10" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M28" s="9" t="inlineStr">
+      <c r="M28" s="10" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N28" s="9" t="inlineStr">
+      <c r="N28" s="10" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O28" s="9" t="inlineStr">
+      <c r="O28" s="10" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P28" s="9" t="inlineStr">
+      <c r="P28" s="10" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q28" s="9" t="inlineStr">
+      <c r="Q28" s="10" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="204" customHeight="1">
-      <c r="B29" s="10" t="inlineStr">
+    <row r="29" ht="171" customHeight="1">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>Responsible investments</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Achieve net zero financed emissions for the University’s investment portfolio by 2050.</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Continuous improvement of the reporting of the University’s sustainability-related investment profile metrics, could include investment in climate mitigation and transition solutions, and compliance with related obligations (eg UNPRI).</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 12b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Report on relevant sustainability-related investment portfolio metrics and report on how the University has complied with its related obligations
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Report on relevant sustainability-related investment portfolio metrics and report on how the University has complied with its related obligations
+In end-2025 reporting your area reported on the related SP2030 target 12b(i) (click the ref in Column H to see it in full in Tab 3).
 Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G29" s="13" t="inlineStr">
         <is>
           <t>We will report on sustainability-related investment portfolio metrics and the University's compliance with related obligations (e.g. UNPRI) in the Responsible investments section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H29" s="15" t="inlineStr">
         <is>
           <t>12b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I29" s="12" t="inlineStr">
+      <c r="I29" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J29" s="12" t="inlineStr">
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>Since 2022 the University has published its sustainability-related investment portfolio metrics including carbon intensity. Historically this has only applied to Australian &amp; International equities, but from this year we are able to also include Fixed Income &amp; Credit. Other asset classes will be included as the data relating to them becomes available and is considered reasonable. 
 While data and metrics are continuously being refined, we have met our target of enhanced transparent reporting of the investment portfolio.</t>
         </is>
       </c>
-      <c r="K29" s="12" t="inlineStr"/>
-      <c r="L29" s="13" t="n"/>
-      <c r="M29" s="13" t="n"/>
-      <c r="N29" s="13" t="n"/>
-      <c r="O29" s="13" t="n"/>
-      <c r="P29" s="13" t="n"/>
-      <c r="Q29" s="13" t="n"/>
+      <c r="K29" s="13" t="inlineStr"/>
+      <c r="L29" s="14" t="n"/>
+      <c r="M29" s="14" t="n"/>
+      <c r="N29" s="14" t="n"/>
+      <c r="O29" s="14" t="n"/>
+      <c r="P29" s="14" t="n"/>
+      <c r="Q29" s="14" t="n"/>
     </row>
     <row r="30"/>
   </sheetData>
@@ -1343,6 +1508,7 @@
     <hyperlink ref="H29" location="'3. SR25 responses'!B22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1352,7 +1518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1365,104 +1531,148 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4"/>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Thursday 24 December 2026 (Christmas shutdown) (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="39" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="18" t="inlineStr"/>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1470,6 +1680,7 @@
     <mergeCell ref="C5:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1479,7 +1690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1491,127 +1702,172 @@
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Your SR25 responses – Chief Finance Officer Group (CFOG)</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Procurement</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>The University has curated living labs covering the priority areas of this Plan</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Please describe any activities in Procurement which address sustainability issues via collaboration between academic and professional staff.</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr"/>
-      <c r="G7" s="12" t="inlineStr"/>
-      <c r="H7" s="12" t="inlineStr"/>
-      <c r="I7" s="12" t="inlineStr"/>
+      <c r="F7" s="13" t="inlineStr"/>
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr"/>
     </row>
     <row r="8" ht="254" customHeight="1">
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>11a(iii)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>The University has reduced waste to landfill to 10kg per person</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Case studies on end of life pathways for specialist university waste streams in 2025 (e.g. the lab equipment auction organised by Procurement c. 2023)</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Not provided (as agreed with Sustainability Strategy team)</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>From Jose:
 At the moment we do not track any reduction of waste in our operation. 
@@ -1621,62 +1877,62 @@
 In our space Tom Atta or Peter Sritharan would be able to confirm or guide internally who to talk to to confirm this initiative. The potential suppliers that are doing this are CompNow and/or Citadel or others in the AV Space.</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr"/>
-      <c r="H8" s="12" t="inlineStr"/>
-      <c r="I8" s="12" t="inlineStr"/>
+      <c r="G8" s="13" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr"/>
     </row>
     <row r="9" ht="160" customHeight="1">
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>11b(iv)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>The University has reduced the flow and improved the circularity of materials passing through the University</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Case studies demonstrating waste and/or circular economy innovation</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Not provided (as agreed with Sustainability Strategy team)</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>RH note: Not provided, but not critical for reporting.</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr"/>
-      <c r="H9" s="12" t="inlineStr"/>
-      <c r="I9" s="12" t="inlineStr"/>
+      <c r="G9" s="13" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr"/>
+      <c r="I9" s="13" t="inlineStr"/>
     </row>
     <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>11c(i)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>The University has principles for ethical and sustainable consumption and service provision embedded into operations and procurement practices</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Link to Annual Modern Slavery Statement; case study excerpt</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>From Matt (20/1/26): Link to Annual Modern Slavery Statement; case study excerpt
 Link: https://modernslaveryregister.gov.au/statements/22714/
@@ -1684,101 +1940,101 @@
 In regard to what new information we are Ok with publishing on MS in regard to 2025 our approach is to collate this and have it approved for external consumption via this process.</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr"/>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="G10" s="13" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>MS1(a)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="160" customHeight="1">
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>11c(ii)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>The University has principles for ethical and sustainable consumption and service provision embedded into operations and procurement practices</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>List of Fair Trade and other relevant third-party certifications</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Not provided (as agreed with Sustainability Strategy team)</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>RH note: Not provided, but not critical for reporting</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr"/>
-      <c r="H11" s="12" t="inlineStr"/>
-      <c r="I11" s="12" t="inlineStr"/>
+      <c r="G11" s="13" t="inlineStr"/>
+      <c r="H11" s="13" t="inlineStr"/>
+      <c r="I11" s="13" t="inlineStr"/>
     </row>
     <row r="12" ht="160" customHeight="1">
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>11c(iii)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>The University has principles for ethical and sustainable consumption and service provision embedded into operations and procurement practices</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Description of the process for integrating supplier code of conduct into procurement practices, and key outcomes from this process.</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>From Matt (20/1/26): This has not changed from prior years, are you able to use what we submitted last report? (RH note: Yes we can use this).
 From Matt (28/1/26): In 2025 we increased the University’s systemic approach e.g. embedding more outcome focus questions in tenders, enhancing Modern Slavery clauses, implementing a system approach to collecting subcontracted impact spend.</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr"/>
-      <c r="H12" s="12" t="inlineStr"/>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr"/>
+      <c r="H12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>RP1(a)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="320" customHeight="1">
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>11d</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>The University tracks spend with social and Indigenous suppliers, setting targets from 2024</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Dollars spent with suppliers that are classified as social and/or Indigenous supplies (for example, demonstrated by listings on Supply Nation, Social Traders etc) as a percentage of total spend</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>From Matt (20/1/26): As mentioned, due to integration issues with the ERP rollout we will only get direct spend data information at the end of this month (I don’t have an exact ETA yet).
 For the indirect spend (Indigenous/ Social impact suppliers hired via our primary suppliers) this is collated quarterly and Jase is planning on having the 2025 total figures in the next 3 weeks (the construction industry shuts down over Dec/Jan and so we have slower response times). 
@@ -1786,9 +2042,9 @@
 From Matt (28/1/26): What we need to get better at is getting closer to hitting our Indigenous and Social impact spend target (3% by 2030). We have recently created an Indigenous Procurement Working Group made up of key University decision makers to better enable progress in this area.</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr"/>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr"/>
+      <c r="H13" s="13" t="inlineStr"/>
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>RP2(a), RP2(b)</t>
         </is>
@@ -1796,322 +2052,322 @@
     </row>
     <row r="14"/>
     <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="160" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>8a(i)</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Assessment based on the Climate Change Preparedness Framework</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr"/>
-      <c r="G17" s="12" t="inlineStr"/>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="12" t="inlineStr"/>
+      <c r="F17" s="13" t="inlineStr"/>
+      <c r="G17" s="13" t="inlineStr"/>
+      <c r="H17" s="13" t="inlineStr"/>
+      <c r="I17" s="13" t="inlineStr"/>
     </row>
     <row r="18" ht="160" customHeight="1">
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>8a(ii)</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Please provide commentary regarding the Portfolio/team's level of climate change preparedness. Refer to the Climate Change Preparedness Framework for guidance: https://www.unimelb.edu.au/sustainabilityreport/domain-3-walking-the-talk-in-our-operations/climate-resilience#progress-1</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr"/>
-      <c r="G18" s="12" t="inlineStr"/>
-      <c r="H18" s="12" t="inlineStr"/>
-      <c r="I18" s="12" t="inlineStr"/>
+      <c r="F18" s="13" t="inlineStr"/>
+      <c r="G18" s="13" t="inlineStr"/>
+      <c r="H18" s="13" t="inlineStr"/>
+      <c r="I18" s="13" t="inlineStr"/>
     </row>
     <row r="19"/>
     <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>Treasury and Investments</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="188" customHeight="1">
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>12b(i)</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Enhanced transparent reporting of the University’s investment portfolio</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Report on relevant sustainability-related investment portfolio metrics, including carbon intensity</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>Since 2022 the University has published its sustainability-related investment portfolio metrics including carbon intensity. Historically this has only applied to Australian &amp; International equities, but from this year we are able to also include Fixed Income &amp; Credit. Other asset classes will be included as the data relating to them becomes available and is considered reasonable. 
 While data and metrics are continuously being refined, we have met our target of enhanced transparent reporting of the investment portfolio.</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr"/>
-      <c r="H22" s="12" t="inlineStr"/>
-      <c r="I22" s="12" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr"/>
+      <c r="H22" s="13" t="inlineStr"/>
+      <c r="I22" s="13" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="160" customHeight="1">
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>12b(ii)</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Enhanced transparent reporting of the University’s investment portfolio</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Reporting on how the University has complied with its related obligations</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>We have met the targets we set out to achieve in 2022 by being more transparent in our reporting.</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr"/>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="12" t="inlineStr"/>
+      <c r="G23" s="13" t="inlineStr"/>
+      <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr"/>
     </row>
     <row r="24"/>
     <row r="25" ht="30" customHeight="1">
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>Enterprise Portfolio and Investments</t>
         </is>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="160" customHeight="1">
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>8a(i)</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>Assessment based on the Climate Change Preparedness Framework</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr"/>
-      <c r="G27" s="12" t="inlineStr"/>
-      <c r="H27" s="12" t="inlineStr"/>
-      <c r="I27" s="12" t="inlineStr"/>
+      <c r="F27" s="13" t="inlineStr"/>
+      <c r="G27" s="13" t="inlineStr"/>
+      <c r="H27" s="13" t="inlineStr"/>
+      <c r="I27" s="13" t="inlineStr"/>
     </row>
     <row r="28" ht="160" customHeight="1">
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>8a(ii)</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Please provide commentary regarding the Portfolio/team's level of climate change preparedness. Refer to the Climate Change Preparedness Framework for guidance: https://www.unimelb.edu.au/sustainabilityreport/domain-3-walking-the-talk-in-our-operations/climate-resilience#progress-1</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr"/>
-      <c r="G28" s="12" t="inlineStr"/>
-      <c r="H28" s="12" t="inlineStr"/>
-      <c r="I28" s="12" t="inlineStr"/>
+      <c r="F28" s="13" t="inlineStr"/>
+      <c r="G28" s="13" t="inlineStr"/>
+      <c r="H28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2121,6 +2377,7 @@
     <hyperlink ref="B4" location="'1. Reporting template'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2130,7 +2387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2148,1343 +2405,1382 @@
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Quantitative data – Chief Finance Officer Group (CFOG)</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>These figures feed the Sustainability Databook (the University's authoritative quantitative source). Previous years are shown for context – please do not alter. Please provide the CY2026 value (provisional or year-to-date figures are fine; we will confirm final figures with you in January–February), the data source, and any change to definition or boundary. Due: Tuesday 15 December 2026.</t>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>These figures feed the Sustainability Databook (the University's authoritative quantitative source). Previous years are shown for context – please do not alter. Please provide the CY2026 value (provisional or year-to-date figures are fine; we will confirm final figures with you in January–February), the data source, and any change to definition or boundary. Due: Thursday 24 December 2026 (Christmas shutdown).</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5" ht="27" customHeight="1">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Context only (please do not alter)</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Please fill in these cells</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>CY2023</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>CY2024</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>CY2025</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>CY2026 value</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>Data source (file name, link or system)</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>Change to definition or boundary?</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>Notes / limitations</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="9" t="inlineStr">
         <is>
           <t>Useful case studies</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>No instructions – context only.</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr"/>
-      <c r="I7" s="21" t="inlineStr"/>
-      <c r="J7" s="21" t="inlineStr"/>
-      <c r="K7" s="21" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr"/>
+      <c r="D7" s="22" t="inlineStr"/>
+      <c r="E7" s="22" t="inlineStr"/>
+      <c r="F7" s="22" t="inlineStr"/>
+      <c r="G7" s="22" t="inlineStr"/>
+      <c r="H7" s="22" t="inlineStr"/>
+      <c r="I7" s="22" t="inlineStr"/>
+      <c r="J7" s="22" t="inlineStr"/>
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>Please enter numerical values</t>
         </is>
       </c>
-      <c r="L7" s="21" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>Please provide a file name or link to the data source</t>
         </is>
       </c>
-      <c r="M7" s="21" t="inlineStr">
+      <c r="M7" s="22" t="inlineStr">
         <is>
           <t>Describe any change since last year (or 'No change')</t>
         </is>
       </c>
-      <c r="N7" s="21" t="inlineStr">
+      <c r="N7" s="22" t="inlineStr">
         <is>
           <t>Please add any additional notes here</t>
         </is>
       </c>
-      <c r="O7" s="21" t="inlineStr">
+      <c r="O7" s="22" t="inlineStr">
         <is>
           <t>Please provide information on any useful case studies</t>
         </is>
       </c>
     </row>
     <row r="8" ht="39" customHeight="1">
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>RP2(a)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Percentage of Indigeneous spend of total addressable procurement spend</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Total procurement spending</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F8" s="22" t="n"/>
-      <c r="G8" s="22" t="n"/>
-      <c r="H8" s="22" t="n"/>
-      <c r="I8" s="22" t="n"/>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="n"/>
+      <c r="I8" s="23" t="n"/>
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="n"/>
-      <c r="M8" s="13" t="n"/>
-      <c r="N8" s="13" t="n"/>
-      <c r="O8" s="13" t="n"/>
+      <c r="K8" s="14" t="n"/>
+      <c r="L8" s="14" t="n"/>
+      <c r="M8" s="14" t="n"/>
+      <c r="N8" s="14" t="n"/>
+      <c r="O8" s="14" t="n"/>
     </row>
     <row r="9" ht="39" customHeight="1">
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>RP2(a)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr"/>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Total Indigeneous spending</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F9" s="22" t="n"/>
-      <c r="G9" s="22" t="n"/>
-      <c r="H9" s="22" t="n"/>
-      <c r="I9" s="22" t="n"/>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="23" t="n"/>
+      <c r="H9" s="23" t="n"/>
+      <c r="I9" s="23" t="n"/>
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="12" t="n"/>
+      <c r="K9" s="13" t="n"/>
+      <c r="L9" s="13" t="n"/>
+      <c r="M9" s="13" t="n"/>
+      <c r="N9" s="13" t="n"/>
+      <c r="O9" s="13" t="n"/>
     </row>
     <row r="10" ht="39" customHeight="1">
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>RP2(a)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr"/>
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Percentage of Indigeneous spend of total addressable procurement spend</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="22" t="n"/>
-      <c r="H10" s="22" t="n"/>
-      <c r="I10" s="22" t="n"/>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="23" t="n"/>
+      <c r="H10" s="23" t="n"/>
+      <c r="I10" s="23" t="n"/>
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="12" t="n"/>
-      <c r="O10" s="12" t="n"/>
+      <c r="K10" s="13" t="n"/>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13" t="n"/>
+      <c r="N10" s="13" t="n"/>
+      <c r="O10" s="13" t="n"/>
     </row>
     <row r="11" ht="39" customHeight="1">
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>RP2(b)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Percentage of social spend of total addressable procurement spend</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Total procurement spending</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F11" s="22" t="n"/>
-      <c r="G11" s="22" t="n"/>
-      <c r="H11" s="22" t="n"/>
-      <c r="I11" s="22" t="n"/>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="23" t="n"/>
+      <c r="H11" s="23" t="n"/>
+      <c r="I11" s="23" t="n"/>
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K11" s="13" t="n"/>
-      <c r="L11" s="13" t="n"/>
-      <c r="M11" s="13" t="n"/>
-      <c r="N11" s="13" t="n"/>
-      <c r="O11" s="13" t="n"/>
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="14" t="n"/>
+      <c r="N11" s="14" t="n"/>
+      <c r="O11" s="14" t="n"/>
     </row>
     <row r="12" ht="39" customHeight="1">
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>RP2(b)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr"/>
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Total social spending</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F12" s="22" t="n"/>
-      <c r="G12" s="22" t="n"/>
-      <c r="H12" s="22" t="n"/>
-      <c r="I12" s="22" t="n"/>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="23" t="n"/>
+      <c r="H12" s="23" t="n"/>
+      <c r="I12" s="23" t="n"/>
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
-      <c r="N12" s="12" t="n"/>
-      <c r="O12" s="12" t="n"/>
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="13" t="n"/>
+      <c r="N12" s="13" t="n"/>
+      <c r="O12" s="13" t="n"/>
     </row>
     <row r="13" ht="39" customHeight="1">
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>RP2(b)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr"/>
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Percentage of Indigeneous spend of total addressable procurement spend</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F13" s="22" t="n"/>
-      <c r="G13" s="22" t="n"/>
-      <c r="H13" s="22" t="n"/>
-      <c r="I13" s="22" t="n"/>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="23" t="n"/>
+      <c r="H13" s="23" t="n"/>
+      <c r="I13" s="23" t="n"/>
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
-      <c r="N13" s="12" t="n"/>
-      <c r="O13" s="12" t="n"/>
+      <c r="K13" s="13" t="n"/>
+      <c r="L13" s="13" t="n"/>
+      <c r="M13" s="13" t="n"/>
+      <c r="N13" s="13" t="n"/>
+      <c r="O13" s="13" t="n"/>
     </row>
     <row r="14" ht="105" customHeight="1">
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>RI1(a)</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>Annual monitoring and reporting on the investment portfolio's net zero transition progress, including tracking the percentage of AUM managed by investment managers aligned with (or commited to net zero by 2050</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Total Asset Under Management (AUM)</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F14" s="22" t="n"/>
-      <c r="G14" s="22" t="n"/>
-      <c r="H14" s="22" t="n"/>
-      <c r="I14" s="22" t="n"/>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="23" t="n"/>
+      <c r="H14" s="23" t="n"/>
+      <c r="I14" s="23" t="n"/>
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K14" s="13" t="n"/>
-      <c r="L14" s="13" t="n"/>
-      <c r="M14" s="13" t="n"/>
-      <c r="N14" s="13" t="n"/>
-      <c r="O14" s="13" t="n"/>
+      <c r="K14" s="14" t="n"/>
+      <c r="L14" s="14" t="n"/>
+      <c r="M14" s="14" t="n"/>
+      <c r="N14" s="14" t="n"/>
+      <c r="O14" s="14" t="n"/>
     </row>
     <row r="15" ht="39" customHeight="1">
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>RI1(a)</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr"/>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr"/>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>AUM managed by Investment Managers aligned with net zero commitment</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F15" s="22" t="n"/>
-      <c r="G15" s="22" t="n"/>
-      <c r="H15" s="22" t="n"/>
-      <c r="I15" s="22" t="n"/>
-      <c r="J15" s="12" t="inlineStr">
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="23" t="n"/>
+      <c r="I15" s="23" t="n"/>
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
-      <c r="N15" s="12" t="n"/>
-      <c r="O15" s="12" t="n"/>
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="13" t="n"/>
+      <c r="M15" s="13" t="n"/>
+      <c r="N15" s="13" t="n"/>
+      <c r="O15" s="13" t="n"/>
     </row>
     <row r="16" ht="39" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>RI1(a)</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr"/>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr"/>
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Percentage of AUM managed by Investment Managers aligned with net zero commitment</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F16" s="22" t="n"/>
-      <c r="G16" s="22" t="n"/>
-      <c r="H16" s="22" t="n"/>
-      <c r="I16" s="22" t="n"/>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="F16" s="23" t="n"/>
+      <c r="G16" s="23" t="n"/>
+      <c r="H16" s="23" t="n"/>
+      <c r="I16" s="23" t="n"/>
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
-      <c r="M16" s="12" t="n"/>
-      <c r="N16" s="12" t="n"/>
-      <c r="O16" s="12" t="n"/>
+      <c r="K16" s="13" t="n"/>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="13" t="n"/>
+      <c r="N16" s="13" t="n"/>
+      <c r="O16" s="13" t="n"/>
     </row>
     <row r="17" ht="122" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Continuous improvement of the reporting of the University's sustainability-related investment profile metrics, including investment in climate mitigation and transition solutions, and compliance with related obligations (e.g. UNPRI)</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Total Asset Under Management (AUM)</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F17" s="22" t="n"/>
-      <c r="G17" s="22" t="n"/>
-      <c r="H17" s="22" t="n"/>
-      <c r="I17" s="22" t="n"/>
-      <c r="J17" s="12" t="inlineStr">
+      <c r="F17" s="23" t="n"/>
+      <c r="G17" s="23" t="n"/>
+      <c r="H17" s="23" t="n"/>
+      <c r="I17" s="23" t="n"/>
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K17" s="13" t="n"/>
-      <c r="L17" s="13" t="n"/>
-      <c r="M17" s="13" t="n"/>
-      <c r="N17" s="13" t="n"/>
-      <c r="O17" s="13" t="n"/>
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="14" t="n"/>
     </row>
     <row r="18" ht="39" customHeight="1">
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr"/>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr"/>
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>AUM invested in climate/transition solution</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="F18" s="22" t="n"/>
-      <c r="G18" s="22" t="n"/>
-      <c r="H18" s="22" t="n"/>
-      <c r="I18" s="22" t="n"/>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="F18" s="23" t="n"/>
+      <c r="G18" s="23" t="n"/>
+      <c r="H18" s="23" t="n"/>
+      <c r="I18" s="23" t="n"/>
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
-      <c r="N18" s="12" t="n"/>
-      <c r="O18" s="12" t="n"/>
+      <c r="K18" s="13" t="n"/>
+      <c r="L18" s="13" t="n"/>
+      <c r="M18" s="13" t="n"/>
+      <c r="N18" s="13" t="n"/>
+      <c r="O18" s="13" t="n"/>
     </row>
     <row r="19" ht="39" customHeight="1">
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr"/>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr"/>
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Percentage of AUM invested in climate/transition solution</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F19" s="22" t="n"/>
-      <c r="G19" s="22" t="n"/>
-      <c r="H19" s="22" t="n"/>
-      <c r="I19" s="22" t="n"/>
-      <c r="J19" s="12" t="inlineStr">
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="23" t="n"/>
+      <c r="H19" s="23" t="n"/>
+      <c r="I19" s="23" t="n"/>
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K19" s="12" t="n"/>
-      <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
-      <c r="N19" s="12" t="n"/>
-      <c r="O19" s="12" t="n"/>
+      <c r="K19" s="13" t="n"/>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="13" t="n"/>
+      <c r="N19" s="13" t="n"/>
+      <c r="O19" s="13" t="n"/>
     </row>
     <row r="20" ht="39" customHeight="1">
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr"/>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr"/>
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Estimated UoM absolute financed carbon emissions</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F20" s="22" t="n"/>
-      <c r="G20" s="22" t="n">
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="23" t="n">
         <v>121733</v>
       </c>
-      <c r="H20" s="22" t="n">
+      <c r="H20" s="23" t="n">
         <v>111919</v>
       </c>
-      <c r="I20" s="22" t="n">
+      <c r="I20" s="23" t="n">
         <v>123381</v>
       </c>
-      <c r="J20" s="12" t="inlineStr">
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K20" s="12" t="n"/>
-      <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
-      <c r="N20" s="12" t="n"/>
-      <c r="O20" s="12" t="n"/>
+      <c r="K20" s="13" t="n"/>
+      <c r="L20" s="13" t="n"/>
+      <c r="M20" s="13" t="n"/>
+      <c r="N20" s="13" t="n"/>
+      <c r="O20" s="13" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr"/>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr"/>
+      <c r="D21" s="24" t="inlineStr">
         <is>
           <t>Australian Equities</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F21" s="22" t="n"/>
-      <c r="G21" s="22" t="n">
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="23" t="n">
         <v>101663</v>
       </c>
-      <c r="H21" s="22" t="n">
+      <c r="H21" s="23" t="n">
         <v>82052</v>
       </c>
-      <c r="I21" s="22" t="n">
+      <c r="I21" s="23" t="n">
         <v>57483</v>
       </c>
-      <c r="J21" s="12" t="inlineStr">
+      <c r="J21" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
-      <c r="N21" s="12" t="n"/>
-      <c r="O21" s="12" t="n"/>
+      <c r="K21" s="13" t="n"/>
+      <c r="L21" s="13" t="n"/>
+      <c r="M21" s="13" t="n"/>
+      <c r="N21" s="13" t="n"/>
+      <c r="O21" s="13" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr"/>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr"/>
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>International Equities</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F22" s="22" t="n"/>
-      <c r="G22" s="22" t="n">
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="23" t="n">
         <v>20070</v>
       </c>
-      <c r="H22" s="22" t="n">
+      <c r="H22" s="23" t="n">
         <v>29867</v>
       </c>
-      <c r="I22" s="22" t="n">
+      <c r="I22" s="23" t="n">
         <v>27910</v>
       </c>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K22" s="12" t="n"/>
-      <c r="L22" s="12" t="n"/>
-      <c r="M22" s="12" t="n"/>
-      <c r="N22" s="12" t="n"/>
-      <c r="O22" s="12" t="n"/>
+      <c r="K22" s="13" t="n"/>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="13" t="n"/>
+      <c r="N22" s="13" t="n"/>
+      <c r="O22" s="13" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr"/>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr"/>
+      <c r="D23" s="24" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F23" s="22" t="n"/>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="F23" s="23" t="n"/>
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I23" s="22" t="n">
+      <c r="I23" s="23" t="n">
         <v>9312</v>
       </c>
-      <c r="J23" s="12" t="inlineStr">
+      <c r="J23" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="12" t="n"/>
-      <c r="M23" s="12" t="n"/>
-      <c r="N23" s="12" t="n"/>
-      <c r="O23" s="12" t="n"/>
+      <c r="K23" s="13" t="n"/>
+      <c r="L23" s="13" t="n"/>
+      <c r="M23" s="13" t="n"/>
+      <c r="N23" s="13" t="n"/>
+      <c r="O23" s="13" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr"/>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr"/>
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>Fixed Interest</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F24" s="22" t="n"/>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="F24" s="23" t="n"/>
+      <c r="G24" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H24" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I24" s="22" t="n">
+      <c r="I24" s="23" t="n">
         <v>28676</v>
       </c>
-      <c r="J24" s="12" t="inlineStr">
+      <c r="J24" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="12" t="n"/>
-      <c r="O24" s="12" t="n"/>
+      <c r="K24" s="13" t="n"/>
+      <c r="L24" s="13" t="n"/>
+      <c r="M24" s="13" t="n"/>
+      <c r="N24" s="13" t="n"/>
+      <c r="O24" s="13" t="n"/>
     </row>
     <row r="25" ht="39" customHeight="1">
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr"/>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr"/>
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Estimated UoM absolute financed carbon emissions intensity</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F25" s="22" t="n"/>
-      <c r="G25" s="22" t="n">
+      <c r="F25" s="23" t="n"/>
+      <c r="G25" s="23" t="n">
         <v>55</v>
       </c>
-      <c r="H25" s="22" t="n">
+      <c r="H25" s="23" t="n">
         <v>49</v>
       </c>
-      <c r="I25" s="22" t="n">
+      <c r="I25" s="23" t="n">
         <v>38.2</v>
       </c>
-      <c r="J25" s="12" t="inlineStr">
+      <c r="J25" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="12" t="n"/>
-      <c r="M25" s="12" t="n"/>
-      <c r="N25" s="12" t="n"/>
-      <c r="O25" s="12" t="n"/>
+      <c r="K25" s="13" t="n"/>
+      <c r="L25" s="13" t="n"/>
+      <c r="M25" s="13" t="n"/>
+      <c r="N25" s="13" t="n"/>
+      <c r="O25" s="13" t="n"/>
     </row>
     <row r="26" ht="39" customHeight="1">
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr"/>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr"/>
+      <c r="D26" s="24" t="inlineStr">
         <is>
           <t>Australian Equities</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F26" s="22" t="n"/>
-      <c r="G26" s="22" t="n">
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="23" t="n">
         <v>94</v>
       </c>
-      <c r="H26" s="22" t="n">
+      <c r="H26" s="23" t="n">
         <v>72</v>
       </c>
-      <c r="I26" s="22" t="n">
+      <c r="I26" s="23" t="n">
         <v>52.6</v>
       </c>
-      <c r="J26" s="12" t="inlineStr">
+      <c r="J26" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
-      <c r="M26" s="12" t="n"/>
-      <c r="N26" s="12" t="n"/>
-      <c r="O26" s="12" t="n"/>
+      <c r="K26" s="13" t="n"/>
+      <c r="L26" s="13" t="n"/>
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="13" t="n"/>
+      <c r="O26" s="13" t="n"/>
     </row>
     <row r="27" ht="39" customHeight="1">
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr"/>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr"/>
+      <c r="D27" s="24" t="inlineStr">
         <is>
           <t>International Equities</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F27" s="22" t="n"/>
-      <c r="G27" s="22" t="n">
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="H27" s="22" t="n">
+      <c r="H27" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="I27" s="22" t="n">
+      <c r="I27" s="23" t="n">
         <v>23.4</v>
       </c>
-      <c r="J27" s="12" t="inlineStr">
+      <c r="J27" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="12" t="n"/>
-      <c r="M27" s="12" t="n"/>
-      <c r="N27" s="12" t="n"/>
-      <c r="O27" s="12" t="n"/>
+      <c r="K27" s="13" t="n"/>
+      <c r="L27" s="13" t="n"/>
+      <c r="M27" s="13" t="n"/>
+      <c r="N27" s="13" t="n"/>
+      <c r="O27" s="13" t="n"/>
     </row>
     <row r="28" ht="39" customHeight="1">
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr"/>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr"/>
+      <c r="D28" s="24" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F28" s="22" t="n"/>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="F28" s="23" t="n"/>
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H28" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I28" s="22" t="n">
+      <c r="I28" s="23" t="n">
         <v>43.1</v>
       </c>
-      <c r="J28" s="12" t="inlineStr">
+      <c r="J28" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="12" t="n"/>
-      <c r="M28" s="12" t="n"/>
-      <c r="N28" s="12" t="n"/>
-      <c r="O28" s="12" t="n"/>
+      <c r="K28" s="13" t="n"/>
+      <c r="L28" s="13" t="n"/>
+      <c r="M28" s="13" t="n"/>
+      <c r="N28" s="13" t="n"/>
+      <c r="O28" s="13" t="n"/>
     </row>
     <row r="29" ht="39" customHeight="1">
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr"/>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr"/>
+      <c r="D29" s="24" t="inlineStr">
         <is>
           <t>Fixed Interest</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F29" s="22" t="n"/>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I29" s="22" t="n">
+      <c r="I29" s="23" t="n">
         <v>54.3</v>
       </c>
-      <c r="J29" s="12" t="inlineStr">
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="12" t="n"/>
-      <c r="M29" s="12" t="n"/>
-      <c r="N29" s="12" t="n"/>
-      <c r="O29" s="12" t="n"/>
+      <c r="K29" s="13" t="n"/>
+      <c r="L29" s="13" t="n"/>
+      <c r="M29" s="13" t="n"/>
+      <c r="N29" s="13" t="n"/>
+      <c r="O29" s="13" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr"/>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr"/>
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Benchmark financed carbon emissions</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F30" s="22" t="n"/>
-      <c r="G30" s="22" t="n">
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="23" t="n">
         <v>103250</v>
       </c>
-      <c r="H30" s="22" t="n">
+      <c r="H30" s="23" t="n">
         <v>118609</v>
       </c>
-      <c r="I30" s="22" t="n">
+      <c r="I30" s="23" t="n">
         <v>143399</v>
       </c>
-      <c r="J30" s="12" t="inlineStr">
+      <c r="J30" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="12" t="n"/>
-      <c r="M30" s="12" t="n"/>
-      <c r="N30" s="12" t="n"/>
-      <c r="O30" s="12" t="n"/>
+      <c r="K30" s="13" t="n"/>
+      <c r="L30" s="13" t="n"/>
+      <c r="M30" s="13" t="n"/>
+      <c r="N30" s="13" t="n"/>
+      <c r="O30" s="13" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr"/>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr"/>
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>Australian Equities</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F31" s="22" t="n"/>
-      <c r="G31" s="22" t="n">
+      <c r="F31" s="23" t="n"/>
+      <c r="G31" s="23" t="n">
         <v>62433</v>
       </c>
-      <c r="H31" s="22" t="n">
+      <c r="H31" s="23" t="n">
         <v>76031</v>
       </c>
-      <c r="I31" s="22" t="n">
+      <c r="I31" s="23" t="n">
         <v>49827</v>
       </c>
-      <c r="J31" s="12" t="inlineStr">
+      <c r="J31" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K31" s="12" t="n"/>
-      <c r="L31" s="12" t="n"/>
-      <c r="M31" s="12" t="n"/>
-      <c r="N31" s="12" t="n"/>
-      <c r="O31" s="12" t="n"/>
+      <c r="K31" s="13" t="n"/>
+      <c r="L31" s="13" t="n"/>
+      <c r="M31" s="13" t="n"/>
+      <c r="N31" s="13" t="n"/>
+      <c r="O31" s="13" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr"/>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr"/>
+      <c r="D32" s="24" t="inlineStr">
         <is>
           <t>International Equities</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F32" s="22" t="n"/>
-      <c r="G32" s="22" t="n">
+      <c r="F32" s="23" t="n"/>
+      <c r="G32" s="23" t="n">
         <v>40817</v>
       </c>
-      <c r="H32" s="22" t="n">
+      <c r="H32" s="23" t="n">
         <v>42578</v>
       </c>
-      <c r="I32" s="22" t="n">
+      <c r="I32" s="23" t="n">
         <v>34989</v>
       </c>
-      <c r="J32" s="12" t="inlineStr">
+      <c r="J32" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K32" s="12" t="n"/>
-      <c r="L32" s="12" t="n"/>
-      <c r="M32" s="12" t="n"/>
-      <c r="N32" s="12" t="n"/>
-      <c r="O32" s="12" t="n"/>
+      <c r="K32" s="13" t="n"/>
+      <c r="L32" s="13" t="n"/>
+      <c r="M32" s="13" t="n"/>
+      <c r="N32" s="13" t="n"/>
+      <c r="O32" s="13" t="n"/>
     </row>
     <row r="33" ht="39" customHeight="1">
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr"/>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr"/>
+      <c r="D33" s="24" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F33" s="22" t="n"/>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="F33" s="23" t="n"/>
+      <c r="G33" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="H33" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="I33" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J33" s="12" t="inlineStr">
+      <c r="J33" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="12" t="n"/>
-      <c r="M33" s="12" t="n"/>
-      <c r="N33" s="12" t="n"/>
-      <c r="O33" s="12" t="n"/>
+      <c r="K33" s="13" t="n"/>
+      <c r="L33" s="13" t="n"/>
+      <c r="M33" s="13" t="n"/>
+      <c r="N33" s="13" t="n"/>
+      <c r="O33" s="13" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr"/>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr"/>
+      <c r="D34" s="24" t="inlineStr">
         <is>
           <t>Fixed Interest</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>tCO2-e</t>
         </is>
       </c>
-      <c r="F34" s="22" t="n"/>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="F34" s="23" t="n"/>
+      <c r="G34" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H34" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I34" s="22" t="n">
+      <c r="I34" s="23" t="n">
         <v>58583</v>
       </c>
-      <c r="J34" s="12" t="inlineStr">
+      <c r="J34" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K34" s="12" t="n"/>
-      <c r="L34" s="12" t="n"/>
-      <c r="M34" s="12" t="n"/>
-      <c r="N34" s="12" t="n"/>
-      <c r="O34" s="12" t="n"/>
+      <c r="K34" s="13" t="n"/>
+      <c r="L34" s="13" t="n"/>
+      <c r="M34" s="13" t="n"/>
+      <c r="N34" s="13" t="n"/>
+      <c r="O34" s="13" t="n"/>
     </row>
     <row r="35" ht="39" customHeight="1">
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr"/>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr"/>
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>Benchmark financed carbon emissions intensity</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F35" s="22" t="n"/>
-      <c r="G35" s="22" t="n">
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="23" t="n">
         <v>47</v>
       </c>
-      <c r="H35" s="22" t="n">
+      <c r="H35" s="23" t="n">
         <v>51</v>
       </c>
-      <c r="I35" s="22" t="n">
+      <c r="I35" s="23" t="n">
         <v>48.6</v>
       </c>
-      <c r="J35" s="12" t="inlineStr">
+      <c r="J35" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K35" s="12" t="n"/>
-      <c r="L35" s="12" t="n"/>
-      <c r="M35" s="12" t="n"/>
-      <c r="N35" s="12" t="n"/>
-      <c r="O35" s="12" t="n"/>
+      <c r="K35" s="13" t="n"/>
+      <c r="L35" s="13" t="n"/>
+      <c r="M35" s="13" t="n"/>
+      <c r="N35" s="13" t="n"/>
+      <c r="O35" s="13" t="n"/>
     </row>
     <row r="36" ht="39" customHeight="1">
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr"/>
-      <c r="D36" s="23" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr"/>
+      <c r="D36" s="24" t="inlineStr">
         <is>
           <t>Australian Equities</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F36" s="22" t="n"/>
-      <c r="G36" s="22" t="n">
+      <c r="F36" s="23" t="n"/>
+      <c r="G36" s="23" t="n">
         <v>58</v>
       </c>
-      <c r="H36" s="22" t="n">
+      <c r="H36" s="23" t="n">
         <v>67</v>
       </c>
-      <c r="I36" s="22" t="n">
+      <c r="I36" s="23" t="n">
         <v>45.6</v>
       </c>
-      <c r="J36" s="12" t="inlineStr">
+      <c r="J36" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K36" s="12" t="n"/>
-      <c r="L36" s="12" t="n"/>
-      <c r="M36" s="12" t="n"/>
-      <c r="N36" s="12" t="n"/>
-      <c r="O36" s="12" t="n"/>
+      <c r="K36" s="13" t="n"/>
+      <c r="L36" s="13" t="n"/>
+      <c r="M36" s="13" t="n"/>
+      <c r="N36" s="13" t="n"/>
+      <c r="O36" s="13" t="n"/>
     </row>
     <row r="37" ht="39" customHeight="1">
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr"/>
-      <c r="D37" s="23" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr"/>
+      <c r="D37" s="24" t="inlineStr">
         <is>
           <t>International Equities</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F37" s="22" t="n"/>
-      <c r="G37" s="22" t="n">
+      <c r="F37" s="23" t="n"/>
+      <c r="G37" s="23" t="n">
         <v>36</v>
       </c>
-      <c r="H37" s="22" t="n">
+      <c r="H37" s="23" t="n">
         <v>37</v>
       </c>
-      <c r="I37" s="22" t="n">
+      <c r="I37" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="J37" s="12" t="inlineStr">
+      <c r="J37" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K37" s="12" t="n"/>
-      <c r="L37" s="12" t="n"/>
-      <c r="M37" s="12" t="n"/>
-      <c r="N37" s="12" t="n"/>
-      <c r="O37" s="12" t="n"/>
+      <c r="K37" s="13" t="n"/>
+      <c r="L37" s="13" t="n"/>
+      <c r="M37" s="13" t="n"/>
+      <c r="N37" s="13" t="n"/>
+      <c r="O37" s="13" t="n"/>
     </row>
     <row r="38" ht="39" customHeight="1">
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr"/>
-      <c r="D38" s="23" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr"/>
+      <c r="D38" s="24" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F38" s="22" t="n"/>
-      <c r="G38" s="22" t="inlineStr">
+      <c r="F38" s="23" t="n"/>
+      <c r="G38" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H38" s="22" t="inlineStr">
+      <c r="H38" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I38" s="22" t="inlineStr">
+      <c r="I38" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J38" s="12" t="inlineStr">
+      <c r="J38" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K38" s="12" t="n"/>
-      <c r="L38" s="12" t="n"/>
-      <c r="M38" s="12" t="n"/>
-      <c r="N38" s="12" t="n"/>
-      <c r="O38" s="12" t="n"/>
+      <c r="K38" s="13" t="n"/>
+      <c r="L38" s="13" t="n"/>
+      <c r="M38" s="13" t="n"/>
+      <c r="N38" s="13" t="n"/>
+      <c r="O38" s="13" t="n"/>
     </row>
     <row r="39" ht="39" customHeight="1">
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr"/>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr"/>
+      <c r="D39" s="24" t="inlineStr">
         <is>
           <t>Fixed Interest</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>tCO2-e / AUD m invested</t>
         </is>
       </c>
-      <c r="F39" s="22" t="n"/>
-      <c r="G39" s="22" t="inlineStr">
+      <c r="F39" s="23" t="n"/>
+      <c r="G39" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H39" s="22" t="inlineStr">
+      <c r="H39" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I39" s="22" t="n">
+      <c r="I39" s="23" t="n">
         <v>112.9</v>
       </c>
-      <c r="J39" s="12" t="inlineStr">
+      <c r="J39" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K39" s="12" t="n"/>
-      <c r="L39" s="12" t="n"/>
-      <c r="M39" s="12" t="n"/>
-      <c r="N39" s="12" t="n"/>
-      <c r="O39" s="12" t="n"/>
+      <c r="K39" s="13" t="n"/>
+      <c r="L39" s="13" t="n"/>
+      <c r="M39" s="13" t="n"/>
+      <c r="N39" s="13" t="n"/>
+      <c r="O39" s="13" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -3499,6 +3795,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/output/central_unit_requests/CFOG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CFOG - SR26 sustainability reporting request.xlsx
@@ -733,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R30"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -750,9 +750,9 @@
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -811,7 +811,8 @@
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
-• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
+• Note the source of your information, any limitations and the person closest to the data (Column O)
+• Please return the spreadsheet once it has been reviewed and confirmed by your area's senior lead
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
@@ -850,7 +851,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
@@ -918,17 +919,7 @@
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>Data source and limitations</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>Data owner confirms information is accurate</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>Confirmed by (name, role, date)</t>
+          <t>Data source, limitations and contact person</t>
         </is>
       </c>
     </row>
@@ -960,49 +951,39 @@
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr">
-        <is>
-          <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
-        </is>
-      </c>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>Name, role and date of the person confirming</t>
+          <t>Where did this information come from (system, report, survey)? Note any gaps or limitations, and the person closest to the data we can follow up with.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>TR3(b)</t>
+          <t>NB2(c)</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Transformational research</t>
+          <t>Nature and biodiversity</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
+          <t>Improve our understanding of our supply chain impacts on nature.</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
+          <t>Evidence of prioritised high risk procurement categories or suppliers for nature impact management</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>Please describe any efforts within your Faculty/Portfolio to make research practices more sustainable, could include examples from laboratories, fieldwork, procurement, research travel or infrastructure use. Where available, provide evidence of uptake, resource savings, emissions reductions or other outcomes.</t>
+          <t>Please provide the prioritised high-risk procurement categories and/or suppliers identified for nature-impact management, could include the basis for prioritisation and any risk-management, engagement or mitigation actions undertaken or planned.</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
+          <t>We will report on the high-risk procurement categories or suppliers prioritised for nature-impact management, and related actions, in the 2026 Sustainability Report.</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
@@ -1017,90 +998,97 @@
       <c r="M16" s="14" t="n"/>
       <c r="N16" s="14" t="n"/>
       <c r="O16" s="14" t="n"/>
-      <c r="P16" s="14" t="n"/>
-      <c r="Q16" s="14" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>NB2(c)</t>
+          <t>RP1(a)</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Nature and biodiversity</t>
+          <t>Responsible procurement</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Improve our understanding of our supply chain impacts on nature.</t>
+          <t>Strengthen our ethical and sustainable procurement approach.</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Evidence of prioritised high risk procurement categories or suppliers for nature impact management</t>
+          <t>Case studies of maturity improvement related to responsible procurement process and systems.</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>Please provide the prioritised high-risk procurement categories and/or suppliers identified for nature-impact management, could include the basis for prioritisation and any risk-management, engagement or mitigation actions undertaken or planned.</t>
+          <t>Maturity score if framework established; % procurement staff trained
+In end-2025 reporting your area reported on the related SP2030 target 11c(iii) (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>We will report on the high-risk procurement categories or suppliers prioritised for nature-impact management, and related actions, in the 2026 Sustainability Report.</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>N/A – new indicator</t>
-        </is>
-      </c>
-      <c r="I17" s="13" t="inlineStr"/>
-      <c r="J17" s="13" t="inlineStr"/>
+          <t>We will use case studies (and any maturity score or training data) to show improvement in responsible procurement processes and systems in the 2026 Sustainability Report.</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>11c(iii)
+→ view SR25 response</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <t>From Matt (20/1/26): This has not changed from prior years, are you able to use what we submitted last report? (RH note: Yes we can use this).
+From Matt (28/1/26): In 2025 we increased the University’s systemic approach e.g. embedding more outcome focus questions in tenders, enhancing Modern Slavery clauses, implementing a system approach to collecting subcontracted impact spend.</t>
+        </is>
+      </c>
       <c r="K17" s="13" t="inlineStr"/>
       <c r="L17" s="14" t="n"/>
       <c r="M17" s="14" t="n"/>
       <c r="N17" s="14" t="n"/>
       <c r="O17" s="14" t="n"/>
-      <c r="P17" s="14" t="n"/>
-      <c r="Q17" s="14" t="n"/>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>RP1(a)</t>
+          <t>MS1(a)</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Responsible procurement</t>
+          <t>Modern slavery and human rights</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Strengthen our ethical and sustainable procurement approach.</t>
+          <t>Manage our approach to modern slavery and human rights-related risks and opportunities.</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Case studies of maturity improvement related to responsible procurement process and systems.</t>
+          <t>Annual progress reporting via the Modern Slavery Statement</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>Maturity score if framework established; % procurement staff trained
-In end-2025 reporting your area reported on the related SP2030 target 11c(iii) (click the ref in Column H to see it in full in Tab 3).</t>
+          <t>Annual Modern Slavery Statement, with case studies
+In end-2025 reporting your area reported on the related SP2030 target 11c(i) (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>We will use case studies (and any maturity score or training data) to show improvement in responsible procurement processes and systems in the 2026 Sustainability Report.</t>
+          <t>We will draw on the annual Modern Slavery Statement and case studies to report on the University's approach to modern slavery and human rights risks (timing to be aligned with the Statement).</t>
         </is>
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>11c(iii)
+          <t>11c(i)
 → view SR25 response</t>
         </is>
       </c>
@@ -1111,8 +1099,10 @@
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>From Matt (20/1/26): This has not changed from prior years, are you able to use what we submitted last report? (RH note: Yes we can use this).
-From Matt (28/1/26): In 2025 we increased the University’s systemic approach e.g. embedding more outcome focus questions in tenders, enhancing Modern Slavery clauses, implementing a system approach to collecting subcontracted impact spend.</t>
+          <t>From Matt (20/1/26): Link to Annual Modern Slavery Statement; case study excerpt
+Link: https://modernslaveryregister.gov.au/statements/22714/
+We are currently compiling the 2025 statement which will be published in May (2026). 
+In regard to what new information we are Ok with publishing on MS in regard to 2025 our approach is to collate this and have it approved for external consumption via this process.</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr"/>
@@ -1120,72 +1110,55 @@
       <c r="M18" s="14" t="n"/>
       <c r="N18" s="14" t="n"/>
       <c r="O18" s="14" t="n"/>
-      <c r="P18" s="14" t="n"/>
-      <c r="Q18" s="14" t="n"/>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>MS1(a)</t>
+          <t>EN1(c)</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Modern slavery and human rights</t>
+          <t>Enablers</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Manage our approach to modern slavery and human rights-related risks and opportunities.</t>
+          <t>Enablers</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Annual progress reporting via the Modern Slavery Statement</t>
+          <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>Annual Modern Slavery Statement, with case studies
-In end-2025 reporting your area reported on the related SP2030 target 11c(i) (click the ref in Column H to see it in full in Tab 3).</t>
+          <t>Please provide examples of internal engagement or external partnerships involving your portfolio that contributed to sustainability outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>We will draw on the annual Modern Slavery Statement and case studies to report on the University's approach to modern slavery and human rights risks (timing to be aligned with the Statement).</t>
-        </is>
-      </c>
-      <c r="H19" s="15" t="inlineStr">
-        <is>
-          <t>11c(i)
-→ view SR25 response</t>
-        </is>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
-        <is>
-          <t>From Matt (20/1/26): Link to Annual Modern Slavery Statement; case study excerpt
-Link: https://modernslaveryregister.gov.au/statements/22714/
-We are currently compiling the 2025 statement which will be published in May (2026). 
-In regard to what new information we are Ok with publishing on MS in regard to 2025 our approach is to collate this and have it approved for external consumption via this process.</t>
-        </is>
-      </c>
+          <t>We will report on internal engagement and partnerships contributing to sustainability outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr"/>
+      <c r="J19" s="13" t="inlineStr"/>
       <c r="K19" s="13" t="inlineStr"/>
       <c r="L19" s="14" t="n"/>
       <c r="M19" s="14" t="n"/>
       <c r="N19" s="14" t="n"/>
       <c r="O19" s="14" t="n"/>
-      <c r="P19" s="14" t="n"/>
-      <c r="Q19" s="14" t="n"/>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>EN1(c)</t>
+          <t>EN1(d)</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
@@ -1200,17 +1173,17 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
+          <t>Sustainability objectives integrated into governance and decision‑making processes, supported by transparent reporting.</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
+          <t>Please provide evidence of how sustainability objectives are integrated into governance and decision-making within your portfolio, could include relevant committees, policies, planning or approval processes, accountability mechanisms and examples of transparent reporting.</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
+          <t>We will report on how sustainability is integrated into governance and decision-making across faculties and portfolios, and use responses as a baseline for the governance enabler from 2027.</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
@@ -1225,287 +1198,209 @@
       <c r="M20" s="14" t="n"/>
       <c r="N20" s="14" t="n"/>
       <c r="O20" s="14" t="n"/>
-      <c r="P20" s="14" t="n"/>
-      <c r="Q20" s="14" t="n"/>
-    </row>
-    <row r="21" ht="150" customHeight="1">
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>EN1(d)</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Enablers</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Enablers</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Sustainability objectives integrated into governance and decision‑making processes, supported by transparent reporting.</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>Please provide evidence of how sustainability objectives are integrated into governance and decision-making within your Faculty/Portfolio, could include relevant committees, policies, planning or approval processes, accountability mechanisms and examples of transparent reporting.</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>We will report on how sustainability is integrated into governance and decision-making across faculties and portfolios, and use responses as a baseline for the governance enabler from 2027.</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>N/A – new indicator</t>
-        </is>
-      </c>
-      <c r="I21" s="13" t="inlineStr"/>
-      <c r="J21" s="13" t="inlineStr"/>
-      <c r="K21" s="13" t="inlineStr"/>
-      <c r="L21" s="14" t="n"/>
-      <c r="M21" s="14" t="n"/>
-      <c r="N21" s="14" t="n"/>
-      <c r="O21" s="14" t="n"/>
-      <c r="P21" s="14" t="n"/>
-      <c r="Q21" s="14" t="n"/>
-    </row>
+    </row>
+    <row r="21"/>
     <row r="22"/>
-    <row r="23"/>
-    <row r="24" ht="39" customHeight="1">
-      <c r="B24" s="5" t="inlineStr">
+    <row r="23" ht="39" customHeight="1">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>CFOG – Treasury &amp; Investments</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26" ht="27" customHeight="1">
-      <c r="C26" s="6" t="inlineStr">
+    <row r="24"/>
+    <row r="25" ht="27" customHeight="1">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="B27" s="8" t="inlineStr">
+    <row r="26" ht="42" customHeight="1">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K27" s="8" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L27" s="9" t="inlineStr">
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M27" s="9" t="inlineStr">
+      <c r="M26" s="9" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N27" s="9" t="inlineStr">
+      <c r="N26" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O27" s="9" t="inlineStr">
-        <is>
-          <t>Data source and limitations</t>
-        </is>
-      </c>
-      <c r="P27" s="9" t="inlineStr">
-        <is>
-          <t>Data owner confirms information is accurate</t>
-        </is>
-      </c>
-      <c r="Q27" s="9" t="inlineStr">
-        <is>
-          <t>Confirmed by (name, role, date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="81" customHeight="1">
-      <c r="B28" s="10" t="inlineStr"/>
-      <c r="C28" s="10" t="inlineStr"/>
-      <c r="D28" s="10" t="inlineStr"/>
-      <c r="E28" s="10" t="inlineStr"/>
-      <c r="F28" s="10" t="inlineStr"/>
-      <c r="G28" s="10" t="inlineStr"/>
-      <c r="H28" s="10" t="inlineStr"/>
-      <c r="I28" s="10" t="inlineStr"/>
-      <c r="J28" s="10" t="inlineStr"/>
-      <c r="K28" s="10" t="inlineStr"/>
-      <c r="L28" s="10" t="inlineStr">
+      <c r="O26" s="9" t="inlineStr">
+        <is>
+          <t>Data source, limitations and contact person</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="81" customHeight="1">
+      <c r="B27" s="10" t="inlineStr"/>
+      <c r="C27" s="10" t="inlineStr"/>
+      <c r="D27" s="10" t="inlineStr"/>
+      <c r="E27" s="10" t="inlineStr"/>
+      <c r="F27" s="10" t="inlineStr"/>
+      <c r="G27" s="10" t="inlineStr"/>
+      <c r="H27" s="10" t="inlineStr"/>
+      <c r="I27" s="10" t="inlineStr"/>
+      <c r="J27" s="10" t="inlineStr"/>
+      <c r="K27" s="10" t="inlineStr"/>
+      <c r="L27" s="10" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M28" s="10" t="inlineStr">
+      <c r="M27" s="10" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N28" s="10" t="inlineStr">
+      <c r="N27" s="10" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O28" s="10" t="inlineStr">
-        <is>
-          <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
-        </is>
-      </c>
-      <c r="P28" s="10" t="inlineStr">
-        <is>
-          <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
-        </is>
-      </c>
-      <c r="Q28" s="10" t="inlineStr">
-        <is>
-          <t>Name, role and date of the person confirming</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="171" customHeight="1">
-      <c r="B29" s="11" t="inlineStr">
+      <c r="O27" s="10" t="inlineStr">
+        <is>
+          <t>Where did this information come from (system, report, survey)? Note any gaps or limitations, and the person closest to the data we can follow up with.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="171" customHeight="1">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>RI1(b)</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Responsible investments</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Achieve net zero financed emissions for the University’s investment portfolio by 2050.</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Continuous improvement of the reporting of the University’s sustainability-related investment profile metrics, could include investment in climate mitigation and transition solutions, and compliance with related obligations (eg UNPRI).</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>Report on relevant sustainability-related investment portfolio metrics and report on how the University has complied with its related obligations
 In end-2025 reporting your area reported on the related SP2030 target 12b(i) (click the ref in Column H to see it in full in Tab 3).
 Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>We will report on sustainability-related investment portfolio metrics and the University's compliance with related obligations (e.g. UNPRI) in the Responsible investments section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H29" s="15" t="inlineStr">
+      <c r="H28" s="15" t="inlineStr">
         <is>
           <t>12b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I29" s="13" t="inlineStr">
+      <c r="I28" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J29" s="13" t="inlineStr">
+      <c r="J28" s="13" t="inlineStr">
         <is>
           <t>Since 2022 the University has published its sustainability-related investment portfolio metrics including carbon intensity. Historically this has only applied to Australian &amp; International equities, but from this year we are able to also include Fixed Income &amp; Credit. Other asset classes will be included as the data relating to them becomes available and is considered reasonable. 
 While data and metrics are continuously being refined, we have met our target of enhanced transparent reporting of the investment portfolio.</t>
         </is>
       </c>
-      <c r="K29" s="13" t="inlineStr"/>
-      <c r="L29" s="14" t="n"/>
-      <c r="M29" s="14" t="n"/>
-      <c r="N29" s="14" t="n"/>
-      <c r="O29" s="14" t="n"/>
-      <c r="P29" s="14" t="n"/>
-      <c r="Q29" s="14" t="n"/>
-    </row>
-    <row r="30"/>
+      <c r="K28" s="13" t="inlineStr"/>
+      <c r="L28" s="14" t="n"/>
+      <c r="M28" s="14" t="n"/>
+      <c r="N28" s="14" t="n"/>
+      <c r="O28" s="14" t="n"/>
+    </row>
+    <row r="29"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="6">
+    <mergeCell ref="L13:O13"/>
     <mergeCell ref="B4:C8"/>
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="L26:Q26"/>
+    <mergeCell ref="C25:G25"/>
     <mergeCell ref="C13:G13"/>
     <mergeCell ref="D4:G8"/>
-    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="L25:O25"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="P16:P21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$C$2:$C$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="P29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$C$2:$C$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
-    <hyperlink ref="H18" location="'3. SR25 responses'!B12"/>
-    <hyperlink ref="H19" location="'3. SR25 responses'!B10"/>
-    <hyperlink ref="H29" location="'3. SR25 responses'!B22"/>
+    <hyperlink ref="H17" location="'3. SR25 responses'!B12"/>
+    <hyperlink ref="H18" location="'3. SR25 responses'!B10"/>
+    <hyperlink ref="H28" location="'3. SR25 responses'!B22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
